--- a/research/traditional_assets/database/data/germany/germany_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_computers_peripherals.xlsx
@@ -1510,7 +1510,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1647,22 +1647,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09979092818929844</v>
+        <v>0.09952305540473053</v>
       </c>
       <c r="C2">
-        <v>34.90686462623412</v>
+        <v>34.56894137221474</v>
       </c>
       <c r="D2">
-        <v>30.86686462623412</v>
+        <v>30.88294137221473</v>
       </c>
       <c r="E2">
-        <v>-13.3</v>
+        <v>-12.946</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.354</v>
       </c>
       <c r="G2">
         <v>4.04</v>
@@ -1683,28 +1683,28 @@
         <v>31.53</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0178062</v>
       </c>
       <c r="N2">
-        <v>31.53</v>
+        <v>31.5121938</v>
       </c>
       <c r="O2">
-        <v>9.459</v>
+        <v>9.45365814</v>
       </c>
       <c r="P2">
-        <v>22.071</v>
+        <v>22.05853566</v>
       </c>
       <c r="Q2">
-        <v>27.141</v>
+        <v>27.12853566</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09979092818929844</v>
+        <v>0.1001726822270005</v>
       </c>
       <c r="T2">
-        <v>1.246903653332528</v>
+        <v>1.255720143810636</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>1770.731542945716</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1729,22 +1729,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09952305540473053</v>
+        <v>0.09925518262016263</v>
       </c>
       <c r="C3">
-        <v>34.56894137221474</v>
+        <v>34.23103487379733</v>
       </c>
       <c r="D3">
-        <v>30.88294137221473</v>
+        <v>30.89903487379733</v>
       </c>
       <c r="E3">
-        <v>-12.946</v>
+        <v>-12.592</v>
       </c>
       <c r="F3">
-        <v>0.354</v>
+        <v>0.7080000000000001</v>
       </c>
       <c r="G3">
         <v>4.04</v>
@@ -1765,28 +1765,28 @@
         <v>31.53</v>
       </c>
       <c r="M3">
-        <v>0.0178062</v>
+        <v>0.0356124</v>
       </c>
       <c r="N3">
-        <v>31.5121938</v>
+        <v>31.4943876</v>
       </c>
       <c r="O3">
-        <v>9.45365814</v>
+        <v>9.44831628</v>
       </c>
       <c r="P3">
-        <v>22.05853566</v>
+        <v>22.04607132</v>
       </c>
       <c r="Q3">
-        <v>27.12853566</v>
+        <v>27.11607132</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1001726822270005</v>
+        <v>0.1005622271634313</v>
       </c>
       <c r="T3">
-        <v>1.255720143810636</v>
+        <v>1.264716562665849</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>1770.731542945716</v>
+        <v>885.3657714728577</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1811,22 +1811,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09925518262016263</v>
+        <v>0.09898730983559474</v>
       </c>
       <c r="C4">
-        <v>34.23103487379733</v>
+        <v>33.89314515719026</v>
       </c>
       <c r="D4">
-        <v>30.89903487379733</v>
+        <v>30.91514515719026</v>
       </c>
       <c r="E4">
-        <v>-12.592</v>
+        <v>-12.238</v>
       </c>
       <c r="F4">
-        <v>0.7080000000000001</v>
+        <v>1.062</v>
       </c>
       <c r="G4">
         <v>4.04</v>
@@ -1847,28 +1847,28 @@
         <v>31.53</v>
       </c>
       <c r="M4">
-        <v>0.0356124</v>
+        <v>0.0534186</v>
       </c>
       <c r="N4">
-        <v>31.4943876</v>
+        <v>31.4765814</v>
       </c>
       <c r="O4">
-        <v>9.44831628</v>
+        <v>9.442974420000001</v>
       </c>
       <c r="P4">
-        <v>22.04607132</v>
+        <v>22.03360698</v>
       </c>
       <c r="Q4">
-        <v>27.11607132</v>
+        <v>27.10360698</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1005622271634313</v>
+        <v>0.1009598039542214</v>
       </c>
       <c r="T4">
-        <v>1.264716562665849</v>
+        <v>1.273898474693335</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>885.3657714728577</v>
+        <v>590.2438476485719</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1893,22 +1893,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09898730983559474</v>
+        <v>0.09871943705102684</v>
       </c>
       <c r="C5">
-        <v>33.89314515719026</v>
+        <v>33.55527224865655</v>
       </c>
       <c r="D5">
-        <v>30.91514515719026</v>
+        <v>30.93127224865654</v>
       </c>
       <c r="E5">
-        <v>-12.238</v>
+        <v>-11.884</v>
       </c>
       <c r="F5">
-        <v>1.062</v>
+        <v>1.416</v>
       </c>
       <c r="G5">
         <v>4.04</v>
@@ -1929,28 +1929,28 @@
         <v>31.53</v>
       </c>
       <c r="M5">
-        <v>0.0534186</v>
+        <v>0.0712248</v>
       </c>
       <c r="N5">
-        <v>31.4765814</v>
+        <v>31.4587752</v>
       </c>
       <c r="O5">
-        <v>9.442974420000001</v>
+        <v>9.437632560000001</v>
       </c>
       <c r="P5">
-        <v>22.03360698</v>
+        <v>22.02114264</v>
       </c>
       <c r="Q5">
-        <v>27.10360698</v>
+        <v>27.09114264</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1009598039542214</v>
+        <v>0.1013656635948196</v>
       </c>
       <c r="T5">
-        <v>1.273898474693335</v>
+        <v>1.283271676554726</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>590.2438476485719</v>
+        <v>442.6828857364289</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1975,22 +1975,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09871943705102684</v>
+        <v>0.09845156426645894</v>
       </c>
       <c r="C6">
-        <v>33.55527224865655</v>
+        <v>33.21741617451404</v>
       </c>
       <c r="D6">
-        <v>30.93127224865654</v>
+        <v>30.94741617451405</v>
       </c>
       <c r="E6">
-        <v>-11.884</v>
+        <v>-11.53</v>
       </c>
       <c r="F6">
-        <v>1.416</v>
+        <v>1.77</v>
       </c>
       <c r="G6">
         <v>4.04</v>
@@ -2011,28 +2011,28 @@
         <v>31.53</v>
       </c>
       <c r="M6">
-        <v>0.0712248</v>
+        <v>0.08903100000000001</v>
       </c>
       <c r="N6">
-        <v>31.4587752</v>
+        <v>31.440969</v>
       </c>
       <c r="O6">
-        <v>9.437632560000001</v>
+        <v>9.432290700000001</v>
       </c>
       <c r="P6">
-        <v>22.02114264</v>
+        <v>22.0086783</v>
       </c>
       <c r="Q6">
-        <v>27.09114264</v>
+        <v>27.0786783</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1013656635948196</v>
+        <v>0.1017800676489042</v>
       </c>
       <c r="T6">
-        <v>1.283271676554726</v>
+        <v>1.29284220898162</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>442.6828857364289</v>
+        <v>354.1463085891431</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2057,22 +2057,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09845156426645894</v>
+        <v>0.09818369148189106</v>
       </c>
       <c r="C7">
-        <v>33.21741617451404</v>
+        <v>32.87957696113559</v>
       </c>
       <c r="D7">
-        <v>30.94741617451405</v>
+        <v>30.96357696113559</v>
       </c>
       <c r="E7">
-        <v>-11.53</v>
+        <v>-11.176</v>
       </c>
       <c r="F7">
-        <v>1.77</v>
+        <v>2.124000000000001</v>
       </c>
       <c r="G7">
         <v>4.04</v>
@@ -2093,28 +2093,28 @@
         <v>31.53</v>
       </c>
       <c r="M7">
-        <v>0.08903100000000001</v>
+        <v>0.1068372</v>
       </c>
       <c r="N7">
-        <v>31.440969</v>
+        <v>31.4231628</v>
       </c>
       <c r="O7">
-        <v>9.432290700000001</v>
+        <v>9.42694884</v>
       </c>
       <c r="P7">
-        <v>22.0086783</v>
+        <v>21.99621396</v>
       </c>
       <c r="Q7">
-        <v>27.0786783</v>
+        <v>27.06621396</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1017800676489042</v>
+        <v>0.1022032888105224</v>
       </c>
       <c r="T7">
-        <v>1.29284220898162</v>
+        <v>1.302616369758023</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>354.1463085891431</v>
+        <v>295.1219238242859</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2139,22 +2139,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09818369148189106</v>
+        <v>0.09791581869732317</v>
       </c>
       <c r="C8">
-        <v>32.87957696113559</v>
+        <v>32.54175463494914</v>
       </c>
       <c r="D8">
-        <v>30.96357696113559</v>
+        <v>30.97975463494914</v>
       </c>
       <c r="E8">
-        <v>-11.176</v>
+        <v>-10.822</v>
       </c>
       <c r="F8">
-        <v>2.124</v>
+        <v>2.478</v>
       </c>
       <c r="G8">
         <v>4.04</v>
@@ -2175,28 +2175,28 @@
         <v>31.53</v>
       </c>
       <c r="M8">
-        <v>0.1068372</v>
+        <v>0.1246434</v>
       </c>
       <c r="N8">
-        <v>31.4231628</v>
+        <v>31.4053566</v>
       </c>
       <c r="O8">
-        <v>9.42694884</v>
+        <v>9.42160698</v>
       </c>
       <c r="P8">
-        <v>21.99621396</v>
+        <v>21.98374962</v>
       </c>
       <c r="Q8">
-        <v>27.06621396</v>
+        <v>27.05374962</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1022032888105224</v>
+        <v>0.102635611502498</v>
       </c>
       <c r="T8">
-        <v>1.302616369758023</v>
+        <v>1.31260072754037</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2213,7 +2213,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>295.1219238242859</v>
+        <v>252.9616489922451</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2221,22 +2221,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09791581869732316</v>
+        <v>0.09764794591275526</v>
       </c>
       <c r="C9">
-        <v>32.54175463494914</v>
+        <v>32.20394922243789</v>
       </c>
       <c r="D9">
-        <v>30.97975463494914</v>
+        <v>30.99594922243789</v>
       </c>
       <c r="E9">
-        <v>-10.822</v>
+        <v>-10.468</v>
       </c>
       <c r="F9">
-        <v>2.478000000000001</v>
+        <v>2.832</v>
       </c>
       <c r="G9">
         <v>4.04</v>
@@ -2257,28 +2257,28 @@
         <v>31.53</v>
       </c>
       <c r="M9">
-        <v>0.1246434</v>
+        <v>0.1424496</v>
       </c>
       <c r="N9">
-        <v>31.4053566</v>
+        <v>31.3875504</v>
       </c>
       <c r="O9">
-        <v>9.42160698</v>
+        <v>9.41626512</v>
       </c>
       <c r="P9">
-        <v>21.98374962</v>
+        <v>21.97128528</v>
       </c>
       <c r="Q9">
-        <v>27.05374962</v>
+        <v>27.04128528</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.102635611502498</v>
+        <v>0.1030773325138644</v>
       </c>
       <c r="T9">
-        <v>1.31260072754037</v>
+        <v>1.322802136578855</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>252.961648992245</v>
+        <v>221.3414428682144</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2303,22 +2303,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09764794591275526</v>
+        <v>0.09738007312818737</v>
       </c>
       <c r="C10">
-        <v>32.20394922243789</v>
+        <v>31.86616075014047</v>
       </c>
       <c r="D10">
-        <v>30.99594922243789</v>
+        <v>31.01216075014047</v>
       </c>
       <c r="E10">
-        <v>-10.468</v>
+        <v>-10.114</v>
       </c>
       <c r="F10">
-        <v>2.832</v>
+        <v>3.186</v>
       </c>
       <c r="G10">
         <v>4.04</v>
@@ -2339,28 +2339,28 @@
         <v>31.53</v>
       </c>
       <c r="M10">
-        <v>0.1424496</v>
+        <v>0.1602558</v>
       </c>
       <c r="N10">
-        <v>31.3875504</v>
+        <v>31.3697442</v>
       </c>
       <c r="O10">
-        <v>9.41626512</v>
+        <v>9.410923259999999</v>
       </c>
       <c r="P10">
-        <v>21.97128528</v>
+        <v>21.95882094</v>
       </c>
       <c r="Q10">
-        <v>27.04128528</v>
+        <v>27.02882094</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1030773325138644</v>
+        <v>0.1035287616793268</v>
       </c>
       <c r="T10">
-        <v>1.322802136578855</v>
+        <v>1.333227752409395</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>221.3414428682144</v>
+        <v>196.7479492161906</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2385,22 +2385,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09738007312818737</v>
+        <v>0.09711220034361946</v>
       </c>
       <c r="C11">
-        <v>31.86616075014047</v>
+        <v>31.52838924465103</v>
       </c>
       <c r="D11">
-        <v>31.01216075014047</v>
+        <v>31.02838924465103</v>
       </c>
       <c r="E11">
-        <v>-10.114</v>
+        <v>-9.76</v>
       </c>
       <c r="F11">
-        <v>3.186</v>
+        <v>3.54</v>
       </c>
       <c r="G11">
         <v>4.04</v>
@@ -2421,28 +2421,28 @@
         <v>31.53</v>
       </c>
       <c r="M11">
-        <v>0.1602558</v>
+        <v>0.178062</v>
       </c>
       <c r="N11">
-        <v>31.3697442</v>
+        <v>31.351938</v>
       </c>
       <c r="O11">
-        <v>9.410923259999999</v>
+        <v>9.405581399999999</v>
       </c>
       <c r="P11">
-        <v>21.95882094</v>
+        <v>21.9463566</v>
       </c>
       <c r="Q11">
-        <v>27.02882094</v>
+        <v>27.0163566</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1035287616793268</v>
+        <v>0.1039902226040216</v>
       </c>
       <c r="T11">
-        <v>1.333227752409395</v>
+        <v>1.343885048591724</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>196.7479492161906</v>
+        <v>177.0731542945715</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2467,22 +2467,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09711220034361946</v>
+        <v>0.09684432755905158</v>
       </c>
       <c r="C12">
-        <v>31.52838924465103</v>
+        <v>31.19063473261943</v>
       </c>
       <c r="D12">
-        <v>31.02838924465103</v>
+        <v>31.04463473261943</v>
       </c>
       <c r="E12">
-        <v>-9.76</v>
+        <v>-9.406000000000001</v>
       </c>
       <c r="F12">
-        <v>3.540000000000001</v>
+        <v>3.894000000000001</v>
       </c>
       <c r="G12">
         <v>4.04</v>
@@ -2503,28 +2503,28 @@
         <v>31.53</v>
       </c>
       <c r="M12">
-        <v>0.178062</v>
+        <v>0.1958682</v>
       </c>
       <c r="N12">
-        <v>31.351938</v>
+        <v>31.3341318</v>
       </c>
       <c r="O12">
-        <v>9.405581399999999</v>
+        <v>9.400239539999999</v>
       </c>
       <c r="P12">
-        <v>21.9463566</v>
+        <v>21.93389226</v>
       </c>
       <c r="Q12">
-        <v>27.0163566</v>
+        <v>27.00389226</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1039902226040216</v>
+        <v>0.1044620534371366</v>
       </c>
       <c r="T12">
-        <v>1.343885048591724</v>
+        <v>1.354781834575904</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>177.0731542945715</v>
+        <v>160.9755948132469</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09684432755905158</v>
+        <v>0.09657645477448369</v>
       </c>
       <c r="C13">
-        <v>31.19063473261943</v>
+        <v>30.85289724075138</v>
       </c>
       <c r="D13">
-        <v>31.04463473261943</v>
+        <v>31.06089724075138</v>
       </c>
       <c r="E13">
-        <v>-9.406000000000001</v>
+        <v>-9.052</v>
       </c>
       <c r="F13">
-        <v>3.894000000000001</v>
+        <v>4.248</v>
       </c>
       <c r="G13">
         <v>4.04</v>
@@ -2585,28 +2585,28 @@
         <v>31.53</v>
       </c>
       <c r="M13">
-        <v>0.1958682</v>
+        <v>0.2136744</v>
       </c>
       <c r="N13">
-        <v>31.3341318</v>
+        <v>31.3163256</v>
       </c>
       <c r="O13">
-        <v>9.400239539999999</v>
+        <v>9.39489768</v>
       </c>
       <c r="P13">
-        <v>21.93389226</v>
+        <v>21.92142792</v>
       </c>
       <c r="Q13">
-        <v>27.00389226</v>
+        <v>26.99142792</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1044620534371366</v>
+        <v>0.1049446076982769</v>
       </c>
       <c r="T13">
-        <v>1.354781834575904</v>
+        <v>1.365926274786996</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>160.9755948132469</v>
+        <v>147.560961912143</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2631,22 +2631,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09657645477448369</v>
+        <v>0.09630858198991581</v>
       </c>
       <c r="C14">
-        <v>30.85289724075138</v>
+        <v>30.51517679580856</v>
       </c>
       <c r="D14">
-        <v>31.06089724075138</v>
+        <v>31.07717679580856</v>
       </c>
       <c r="E14">
-        <v>-9.052</v>
+        <v>-8.698</v>
       </c>
       <c r="F14">
-        <v>4.248</v>
+        <v>4.602000000000001</v>
       </c>
       <c r="G14">
         <v>4.04</v>
@@ -2667,28 +2667,28 @@
         <v>31.53</v>
       </c>
       <c r="M14">
-        <v>0.2136744</v>
+        <v>0.2314806</v>
       </c>
       <c r="N14">
-        <v>31.3163256</v>
+        <v>31.2985194</v>
       </c>
       <c r="O14">
-        <v>9.39489768</v>
+        <v>9.38955582</v>
       </c>
       <c r="P14">
-        <v>21.92142792</v>
+        <v>21.90896358</v>
       </c>
       <c r="Q14">
-        <v>26.99142792</v>
+        <v>26.97896358</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1049446076982769</v>
+        <v>0.1054382551608228</v>
       </c>
       <c r="T14">
-        <v>1.365926274786996</v>
+        <v>1.37732690902593</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>147.560961912143</v>
+        <v>136.210118688132</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2713,22 +2713,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09630858198991581</v>
+        <v>0.09604070920534789</v>
       </c>
       <c r="C15">
-        <v>30.51517679580856</v>
+        <v>30.17747342460881</v>
       </c>
       <c r="D15">
-        <v>31.07717679580856</v>
+        <v>31.09347342460881</v>
       </c>
       <c r="E15">
-        <v>-8.698</v>
+        <v>-8.343999999999999</v>
       </c>
       <c r="F15">
-        <v>4.602000000000001</v>
+        <v>4.956000000000001</v>
       </c>
       <c r="G15">
         <v>4.04</v>
@@ -2749,28 +2749,28 @@
         <v>31.53</v>
       </c>
       <c r="M15">
-        <v>0.2314806</v>
+        <v>0.2492868000000001</v>
       </c>
       <c r="N15">
-        <v>31.2985194</v>
+        <v>31.2807132</v>
       </c>
       <c r="O15">
-        <v>9.38955582</v>
+        <v>9.38421396</v>
       </c>
       <c r="P15">
-        <v>21.90896358</v>
+        <v>21.89649924</v>
       </c>
       <c r="Q15">
-        <v>26.97896358</v>
+        <v>26.96649924</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1054382551608228</v>
+        <v>0.1059433827969162</v>
       </c>
       <c r="T15">
-        <v>1.37732690902593</v>
+        <v>1.388992674293676</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>136.210118688132</v>
+        <v>126.4808244961225</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2795,22 +2795,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09604070920534789</v>
+        <v>0.09577283642077999</v>
       </c>
       <c r="C16">
-        <v>30.17747342460881</v>
+        <v>29.83978715402622</v>
       </c>
       <c r="D16">
-        <v>31.09347342460881</v>
+        <v>31.10978715402622</v>
       </c>
       <c r="E16">
-        <v>-8.343999999999999</v>
+        <v>-7.989999999999999</v>
       </c>
       <c r="F16">
-        <v>4.956000000000001</v>
+        <v>5.310000000000001</v>
       </c>
       <c r="G16">
         <v>4.04</v>
@@ -2831,28 +2831,28 @@
         <v>31.53</v>
       </c>
       <c r="M16">
-        <v>0.2492868000000001</v>
+        <v>0.2670930000000001</v>
       </c>
       <c r="N16">
-        <v>31.2807132</v>
+        <v>31.262907</v>
       </c>
       <c r="O16">
-        <v>9.38421396</v>
+        <v>9.378872100000001</v>
       </c>
       <c r="P16">
-        <v>21.89649924</v>
+        <v>21.8840349</v>
       </c>
       <c r="Q16">
-        <v>26.96649924</v>
+        <v>26.9540349</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1059433827969162</v>
+        <v>0.106460395789153</v>
       </c>
       <c r="T16">
-        <v>1.388992674293676</v>
+        <v>1.400932928155957</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>126.4808244961225</v>
+        <v>118.0487695297143</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2877,22 +2877,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09577283642077999</v>
+        <v>0.0955049636362121</v>
       </c>
       <c r="C17">
-        <v>29.83978715402622</v>
+        <v>29.50211801099132</v>
       </c>
       <c r="D17">
-        <v>31.10978715402622</v>
+        <v>31.12611801099132</v>
       </c>
       <c r="E17">
-        <v>-7.99</v>
+        <v>-7.636</v>
       </c>
       <c r="F17">
-        <v>5.31</v>
+        <v>5.664000000000001</v>
       </c>
       <c r="G17">
         <v>4.04</v>
@@ -2913,28 +2913,28 @@
         <v>31.53</v>
       </c>
       <c r="M17">
-        <v>0.267093</v>
+        <v>0.2848992</v>
       </c>
       <c r="N17">
-        <v>31.262907</v>
+        <v>31.2451008</v>
       </c>
       <c r="O17">
-        <v>9.378872100000001</v>
+        <v>9.373530239999999</v>
       </c>
       <c r="P17">
-        <v>21.8840349</v>
+        <v>21.87157056</v>
       </c>
       <c r="Q17">
-        <v>26.9540349</v>
+        <v>26.94157056</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.106460395789153</v>
+        <v>0.1069897186145382</v>
       </c>
       <c r="T17">
-        <v>1.400932928155957</v>
+        <v>1.413157473776864</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2951,7 +2951,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>118.0487695297144</v>
+        <v>110.6707214341072</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2959,22 +2959,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0955049636362121</v>
+        <v>0.09523709085164421</v>
       </c>
       <c r="C18">
-        <v>29.50211801099132</v>
+        <v>29.16446602249124</v>
       </c>
       <c r="D18">
-        <v>31.12611801099132</v>
+        <v>31.14246602249124</v>
       </c>
       <c r="E18">
-        <v>-7.636</v>
+        <v>-7.281999999999999</v>
       </c>
       <c r="F18">
-        <v>5.664000000000001</v>
+        <v>6.018000000000002</v>
       </c>
       <c r="G18">
         <v>4.04</v>
@@ -2995,28 +2995,28 @@
         <v>31.53</v>
       </c>
       <c r="M18">
-        <v>0.2848992</v>
+        <v>0.3027054000000001</v>
       </c>
       <c r="N18">
-        <v>31.2451008</v>
+        <v>31.2272946</v>
       </c>
       <c r="O18">
-        <v>9.373530239999999</v>
+        <v>9.368188379999999</v>
       </c>
       <c r="P18">
-        <v>21.87157056</v>
+        <v>21.85910622</v>
       </c>
       <c r="Q18">
-        <v>26.94157056</v>
+        <v>26.92910622</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1069897186145382</v>
+        <v>0.1075317962068003</v>
       </c>
       <c r="T18">
-        <v>1.413157473776864</v>
+        <v>1.425676586762131</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>110.6707214341072</v>
+        <v>104.1606789968068</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3041,22 +3041,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09523709085164421</v>
+        <v>0.09496921806707631</v>
       </c>
       <c r="C19">
-        <v>29.16446602249124</v>
+        <v>28.82683121556981</v>
       </c>
       <c r="D19">
-        <v>31.14246602249124</v>
+        <v>31.15883121556981</v>
       </c>
       <c r="E19">
-        <v>-7.281999999999999</v>
+        <v>-6.927999999999999</v>
       </c>
       <c r="F19">
-        <v>6.018000000000002</v>
+        <v>6.372000000000002</v>
       </c>
       <c r="G19">
         <v>4.04</v>
@@ -3077,28 +3077,28 @@
         <v>31.53</v>
       </c>
       <c r="M19">
-        <v>0.3027054000000001</v>
+        <v>0.3205116000000001</v>
       </c>
       <c r="N19">
-        <v>31.2272946</v>
+        <v>31.2094884</v>
       </c>
       <c r="O19">
-        <v>9.368188379999999</v>
+        <v>9.36284652</v>
       </c>
       <c r="P19">
-        <v>21.85910622</v>
+        <v>21.84664188</v>
       </c>
       <c r="Q19">
-        <v>26.92910622</v>
+        <v>26.91664188</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1075317962068003</v>
+        <v>0.1080870952037516</v>
       </c>
       <c r="T19">
-        <v>1.425676586762131</v>
+        <v>1.43850104396655</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3115,7 +3115,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>104.1606789968068</v>
+        <v>98.3739746080953</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3123,22 +3123,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09496921806707631</v>
+        <v>0.09470134528250841</v>
       </c>
       <c r="C20">
-        <v>28.82683121556981</v>
+        <v>28.48921361732774</v>
       </c>
       <c r="D20">
-        <v>31.15883121556981</v>
+        <v>31.17521361732774</v>
       </c>
       <c r="E20">
-        <v>-6.928</v>
+        <v>-6.574</v>
       </c>
       <c r="F20">
-        <v>6.372000000000001</v>
+        <v>6.726000000000001</v>
       </c>
       <c r="G20">
         <v>4.04</v>
@@ -3159,28 +3159,28 @@
         <v>31.53</v>
       </c>
       <c r="M20">
-        <v>0.3205116</v>
+        <v>0.3383178</v>
       </c>
       <c r="N20">
-        <v>31.2094884</v>
+        <v>31.1916822</v>
       </c>
       <c r="O20">
-        <v>9.36284652</v>
+        <v>9.35750466</v>
       </c>
       <c r="P20">
-        <v>21.84664188</v>
+        <v>21.83417754</v>
       </c>
       <c r="Q20">
-        <v>26.91664188</v>
+        <v>26.90417754</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1080870952037516</v>
+        <v>0.1086561052870474</v>
       </c>
       <c r="T20">
-        <v>1.43850104396655</v>
+        <v>1.451642154435276</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3197,7 +3197,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>98.37397460809531</v>
+        <v>93.19639699714293</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3205,22 +3205,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09470134528250841</v>
+        <v>0.09443347249794054</v>
       </c>
       <c r="C21">
-        <v>28.48921361732774</v>
+        <v>28.15161325492277</v>
       </c>
       <c r="D21">
-        <v>31.17521361732774</v>
+        <v>31.19161325492277</v>
       </c>
       <c r="E21">
-        <v>-6.574</v>
+        <v>-6.219999999999999</v>
       </c>
       <c r="F21">
-        <v>6.726000000000001</v>
+        <v>7.080000000000002</v>
       </c>
       <c r="G21">
         <v>4.04</v>
@@ -3241,28 +3241,28 @@
         <v>31.53</v>
       </c>
       <c r="M21">
-        <v>0.3383178</v>
+        <v>0.3561240000000001</v>
       </c>
       <c r="N21">
-        <v>31.1916822</v>
+        <v>31.173876</v>
       </c>
       <c r="O21">
-        <v>9.35750466</v>
+        <v>9.3521628</v>
       </c>
       <c r="P21">
-        <v>21.83417754</v>
+        <v>21.8217132</v>
       </c>
       <c r="Q21">
-        <v>26.90417754</v>
+        <v>26.8917132</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1086561052870474</v>
+        <v>0.1092393406224257</v>
       </c>
       <c r="T21">
-        <v>1.451642154435276</v>
+        <v>1.46511179266572</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>93.19639699714293</v>
+        <v>88.53657714728577</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3287,22 +3287,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09443347249794054</v>
+        <v>0.09416559971337266</v>
       </c>
       <c r="C22">
-        <v>28.15161325492277</v>
+        <v>27.81403015556981</v>
       </c>
       <c r="D22">
-        <v>31.19161325492277</v>
+        <v>31.20803015556981</v>
       </c>
       <c r="E22">
-        <v>-6.219999999999999</v>
+        <v>-5.865999999999999</v>
       </c>
       <c r="F22">
-        <v>7.080000000000002</v>
+        <v>7.434000000000002</v>
       </c>
       <c r="G22">
         <v>4.04</v>
@@ -3323,28 +3323,28 @@
         <v>31.53</v>
       </c>
       <c r="M22">
-        <v>0.3561240000000001</v>
+        <v>0.3739302000000001</v>
       </c>
       <c r="N22">
-        <v>31.173876</v>
+        <v>31.1560698</v>
       </c>
       <c r="O22">
-        <v>9.3521628</v>
+        <v>9.346820940000001</v>
       </c>
       <c r="P22">
-        <v>21.8217132</v>
+        <v>21.80924886</v>
       </c>
       <c r="Q22">
-        <v>26.8917132</v>
+        <v>26.87924886</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1092393406224257</v>
+        <v>0.1098373414093325</v>
       </c>
       <c r="T22">
-        <v>1.46511179266572</v>
+        <v>1.478922434395669</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3361,7 +3361,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>88.53657714728577</v>
+        <v>84.32054966408167</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3369,22 +3369,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09416559971337263</v>
+        <v>0.09389772692880473</v>
       </c>
       <c r="C23">
-        <v>27.81403015556981</v>
+        <v>27.47646434654112</v>
       </c>
       <c r="D23">
-        <v>31.20803015556982</v>
+        <v>31.22446434654112</v>
       </c>
       <c r="E23">
-        <v>-5.866</v>
+        <v>-5.512</v>
       </c>
       <c r="F23">
-        <v>7.434000000000001</v>
+        <v>7.788000000000001</v>
       </c>
       <c r="G23">
         <v>4.04</v>
@@ -3405,28 +3405,28 @@
         <v>31.53</v>
       </c>
       <c r="M23">
-        <v>0.3739302</v>
+        <v>0.3917364</v>
       </c>
       <c r="N23">
-        <v>31.1560698</v>
+        <v>31.1382636</v>
       </c>
       <c r="O23">
-        <v>9.346820940000001</v>
+        <v>9.341479080000001</v>
       </c>
       <c r="P23">
-        <v>21.80924886</v>
+        <v>21.79678452</v>
       </c>
       <c r="Q23">
-        <v>26.87924886</v>
+        <v>26.86678452</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1098373414093324</v>
+        <v>0.1104506755497497</v>
       </c>
       <c r="T23">
-        <v>1.478922434395669</v>
+        <v>1.493087195144334</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>84.32054966408168</v>
+        <v>80.48779740662343</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3451,22 +3451,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09389772692880473</v>
+        <v>0.09362985414423684</v>
       </c>
       <c r="C24">
-        <v>27.47646434654112</v>
+        <v>27.1389158551664</v>
       </c>
       <c r="D24">
-        <v>31.22446434654112</v>
+        <v>31.2409158551664</v>
       </c>
       <c r="E24">
-        <v>-5.512</v>
+        <v>-5.157999999999999</v>
       </c>
       <c r="F24">
-        <v>7.788000000000001</v>
+        <v>8.142000000000001</v>
       </c>
       <c r="G24">
         <v>4.04</v>
@@ -3487,28 +3487,28 @@
         <v>31.53</v>
       </c>
       <c r="M24">
-        <v>0.3917364</v>
+        <v>0.4095426</v>
       </c>
       <c r="N24">
-        <v>31.1382636</v>
+        <v>31.1204574</v>
       </c>
       <c r="O24">
-        <v>9.341479080000001</v>
+        <v>9.336137219999999</v>
       </c>
       <c r="P24">
-        <v>21.79678452</v>
+        <v>21.78432018</v>
       </c>
       <c r="Q24">
-        <v>26.86678452</v>
+        <v>26.85432018</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1104506755497497</v>
+        <v>0.1110799404470608</v>
       </c>
       <c r="T24">
-        <v>1.493087195144334</v>
+        <v>1.507619871756601</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>80.48779740662343</v>
+        <v>76.98832795416153</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3533,22 +3533,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09362985414423684</v>
+        <v>0.09336198135966894</v>
       </c>
       <c r="C25">
-        <v>27.1389158551664</v>
+        <v>26.80138470883299</v>
       </c>
       <c r="D25">
-        <v>31.2409158551664</v>
+        <v>31.25738470883299</v>
       </c>
       <c r="E25">
-        <v>-5.157999999999999</v>
+        <v>-4.803999999999998</v>
       </c>
       <c r="F25">
-        <v>8.142000000000001</v>
+        <v>8.496000000000002</v>
       </c>
       <c r="G25">
         <v>4.04</v>
@@ -3569,28 +3569,28 @@
         <v>31.53</v>
       </c>
       <c r="M25">
-        <v>0.4095426</v>
+        <v>0.4273488000000001</v>
       </c>
       <c r="N25">
-        <v>31.1204574</v>
+        <v>31.1026512</v>
       </c>
       <c r="O25">
-        <v>9.336137219999999</v>
+        <v>9.33079536</v>
       </c>
       <c r="P25">
-        <v>21.78432018</v>
+        <v>21.77185584</v>
       </c>
       <c r="Q25">
-        <v>26.85432018</v>
+        <v>26.84185584</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1110799404470608</v>
+        <v>0.1117257649469328</v>
       </c>
       <c r="T25">
-        <v>1.507619871756601</v>
+        <v>1.522534987227086</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>76.98832795416153</v>
+        <v>73.78048095607147</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09336198135966894</v>
+        <v>0.09309410857510106</v>
       </c>
       <c r="C26">
-        <v>26.80138470883299</v>
+        <v>26.46387093498603</v>
       </c>
       <c r="D26">
-        <v>31.25738470883299</v>
+        <v>31.27387093498603</v>
       </c>
       <c r="E26">
-        <v>-4.804</v>
+        <v>-4.449999999999999</v>
       </c>
       <c r="F26">
-        <v>8.496</v>
+        <v>8.850000000000001</v>
       </c>
       <c r="G26">
         <v>4.04</v>
@@ -3651,28 +3651,28 @@
         <v>31.53</v>
       </c>
       <c r="M26">
-        <v>0.4273488</v>
+        <v>0.445155</v>
       </c>
       <c r="N26">
-        <v>31.1026512</v>
+        <v>31.084845</v>
       </c>
       <c r="O26">
-        <v>9.33079536</v>
+        <v>9.3254535</v>
       </c>
       <c r="P26">
-        <v>21.77185584</v>
+        <v>21.7593915</v>
       </c>
       <c r="Q26">
-        <v>26.84185584</v>
+        <v>26.8293915</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1117257649469328</v>
+        <v>0.1123888114334681</v>
       </c>
       <c r="T26">
-        <v>1.522534987227086</v>
+        <v>1.537847839110117</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>73.78048095607149</v>
+        <v>70.82926171782862</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3697,22 +3697,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09309410857510106</v>
+        <v>0.09282623579053315</v>
       </c>
       <c r="C27">
-        <v>26.46387093498603</v>
+        <v>26.12637456112856</v>
       </c>
       <c r="D27">
-        <v>31.27387093498603</v>
+        <v>31.29037456112856</v>
       </c>
       <c r="E27">
-        <v>-4.449999999999999</v>
+        <v>-4.095999999999998</v>
       </c>
       <c r="F27">
-        <v>8.850000000000001</v>
+        <v>9.204000000000002</v>
       </c>
       <c r="G27">
         <v>4.04</v>
@@ -3733,28 +3733,28 @@
         <v>31.53</v>
       </c>
       <c r="M27">
-        <v>0.445155</v>
+        <v>0.4629612000000001</v>
       </c>
       <c r="N27">
-        <v>31.084845</v>
+        <v>31.0670388</v>
       </c>
       <c r="O27">
-        <v>9.3254535</v>
+        <v>9.32011164</v>
       </c>
       <c r="P27">
-        <v>21.7593915</v>
+        <v>21.74692716</v>
       </c>
       <c r="Q27">
-        <v>26.8293915</v>
+        <v>26.81692716</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1123888114334681</v>
+        <v>0.1130697780953151</v>
       </c>
       <c r="T27">
-        <v>1.537847839110117</v>
+        <v>1.553574551854852</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>70.82926171782862</v>
+        <v>68.10505934406598</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3779,22 +3779,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09282623579053315</v>
+        <v>0.09255836300596526</v>
       </c>
       <c r="C28">
-        <v>26.12637456112856</v>
+        <v>25.78889561482173</v>
       </c>
       <c r="D28">
-        <v>31.29037456112856</v>
+        <v>31.30689561482173</v>
       </c>
       <c r="E28">
-        <v>-4.095999999999998</v>
+        <v>-3.741999999999999</v>
       </c>
       <c r="F28">
-        <v>9.204000000000002</v>
+        <v>9.558000000000002</v>
       </c>
       <c r="G28">
         <v>4.04</v>
@@ -3815,28 +3815,28 @@
         <v>31.53</v>
       </c>
       <c r="M28">
-        <v>0.4629612000000001</v>
+        <v>0.4807674000000001</v>
       </c>
       <c r="N28">
-        <v>31.0670388</v>
+        <v>31.0492326</v>
       </c>
       <c r="O28">
-        <v>9.32011164</v>
+        <v>9.314769779999999</v>
       </c>
       <c r="P28">
-        <v>21.74692716</v>
+        <v>21.73446282</v>
       </c>
       <c r="Q28">
-        <v>26.81692716</v>
+        <v>26.80446282</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1130697780953151</v>
+        <v>0.1137694013780346</v>
       </c>
       <c r="T28">
-        <v>1.553574551854852</v>
+        <v>1.569732133441908</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>68.10505934406598</v>
+        <v>65.5826497387302</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3861,22 +3861,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09255836300596526</v>
+        <v>0.09229049022139735</v>
       </c>
       <c r="C29">
-        <v>25.78889561482173</v>
+        <v>25.45143412368493</v>
       </c>
       <c r="D29">
-        <v>31.30689561482173</v>
+        <v>31.32343412368493</v>
       </c>
       <c r="E29">
-        <v>-3.741999999999999</v>
+        <v>-3.387999999999998</v>
       </c>
       <c r="F29">
-        <v>9.558000000000002</v>
+        <v>9.912000000000003</v>
       </c>
       <c r="G29">
         <v>4.04</v>
@@ -3897,28 +3897,28 @@
         <v>31.53</v>
       </c>
       <c r="M29">
-        <v>0.4807674000000001</v>
+        <v>0.4985736000000001</v>
       </c>
       <c r="N29">
-        <v>31.0492326</v>
+        <v>31.0314264</v>
       </c>
       <c r="O29">
-        <v>9.314769779999999</v>
+        <v>9.309427919999999</v>
       </c>
       <c r="P29">
-        <v>21.73446282</v>
+        <v>21.72199848</v>
       </c>
       <c r="Q29">
-        <v>26.80446282</v>
+        <v>26.79199848</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1137694013780346</v>
+        <v>0.1144884586408297</v>
       </c>
       <c r="T29">
-        <v>1.569732133441908</v>
+        <v>1.586338536739715</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>65.5826497387302</v>
+        <v>63.24041224806125</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3943,22 +3943,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09229049022139735</v>
+        <v>0.09202261743682945</v>
       </c>
       <c r="C30">
-        <v>25.45143412368493</v>
+        <v>25.11399011539593</v>
       </c>
       <c r="D30">
-        <v>31.32343412368493</v>
+        <v>31.33999011539593</v>
       </c>
       <c r="E30">
-        <v>-3.387999999999998</v>
+        <v>-3.033999999999997</v>
       </c>
       <c r="F30">
-        <v>9.912000000000003</v>
+        <v>10.266</v>
       </c>
       <c r="G30">
         <v>4.04</v>
@@ -3979,28 +3979,28 @@
         <v>31.53</v>
       </c>
       <c r="M30">
-        <v>0.4985736000000001</v>
+        <v>0.5163798000000002</v>
       </c>
       <c r="N30">
-        <v>31.0314264</v>
+        <v>31.0136202</v>
       </c>
       <c r="O30">
-        <v>9.309427919999999</v>
+        <v>9.304086059999999</v>
       </c>
       <c r="P30">
-        <v>21.72199848</v>
+        <v>21.70953414</v>
       </c>
       <c r="Q30">
-        <v>26.79199848</v>
+        <v>26.77953414</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1144884586408297</v>
+        <v>0.115227771037788</v>
       </c>
       <c r="T30">
-        <v>1.586338536739715</v>
+        <v>1.603412726045912</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>63.24041224806125</v>
+        <v>61.05970837743845</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4025,22 +4025,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09202261743682945</v>
+        <v>0.09175474465226158</v>
       </c>
       <c r="C31">
-        <v>25.11399011539593</v>
+        <v>24.77656361769105</v>
       </c>
       <c r="D31">
-        <v>31.33999011539593</v>
+        <v>31.35656361769105</v>
       </c>
       <c r="E31">
-        <v>-3.033999999999999</v>
+        <v>-2.68</v>
       </c>
       <c r="F31">
-        <v>10.266</v>
+        <v>10.62</v>
       </c>
       <c r="G31">
         <v>4.04</v>
@@ -4061,28 +4061,28 @@
         <v>31.53</v>
       </c>
       <c r="M31">
-        <v>0.5163798000000001</v>
+        <v>0.534186</v>
       </c>
       <c r="N31">
-        <v>31.0136202</v>
+        <v>30.995814</v>
       </c>
       <c r="O31">
-        <v>9.304086059999999</v>
+        <v>9.2987442</v>
       </c>
       <c r="P31">
-        <v>21.70953414</v>
+        <v>21.6970698</v>
       </c>
       <c r="Q31">
-        <v>26.77953414</v>
+        <v>26.7670698</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.115227771037788</v>
+        <v>0.115988206646088</v>
       </c>
       <c r="T31">
-        <v>1.603412726045912</v>
+        <v>1.620974749332286</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>61.05970837743846</v>
+        <v>59.02438476485718</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4107,22 +4107,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09175474465226158</v>
+        <v>0.09148687186769366</v>
       </c>
       <c r="C32">
-        <v>24.77656361769105</v>
+        <v>24.43915465836531</v>
       </c>
       <c r="D32">
-        <v>31.35656361769105</v>
+        <v>31.37315465836532</v>
       </c>
       <c r="E32">
-        <v>-2.68</v>
+        <v>-2.325999999999999</v>
       </c>
       <c r="F32">
-        <v>10.62</v>
+        <v>10.974</v>
       </c>
       <c r="G32">
         <v>4.04</v>
@@ -4143,28 +4143,28 @@
         <v>31.53</v>
       </c>
       <c r="M32">
-        <v>0.534186</v>
+        <v>0.5519922</v>
       </c>
       <c r="N32">
-        <v>30.995814</v>
+        <v>30.9780078</v>
       </c>
       <c r="O32">
-        <v>9.2987442</v>
+        <v>9.29340234</v>
       </c>
       <c r="P32">
-        <v>21.6970698</v>
+        <v>21.68460546</v>
       </c>
       <c r="Q32">
-        <v>26.7670698</v>
+        <v>26.75460546</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.115988206646088</v>
+        <v>0.1167706838662227</v>
       </c>
       <c r="T32">
-        <v>1.620974749332286</v>
+        <v>1.639045816771888</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>59.02438476485718</v>
+        <v>57.1203723530876</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4189,22 +4189,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09148687186769366</v>
+        <v>0.09121899908312578</v>
       </c>
       <c r="C33">
-        <v>24.43915465836531</v>
+        <v>24.1017632652726</v>
       </c>
       <c r="D33">
-        <v>31.37315465836532</v>
+        <v>31.3897632652726</v>
       </c>
       <c r="E33">
-        <v>-2.325999999999999</v>
+        <v>-1.972</v>
       </c>
       <c r="F33">
-        <v>10.974</v>
+        <v>11.328</v>
       </c>
       <c r="G33">
         <v>4.04</v>
@@ -4225,28 +4225,28 @@
         <v>31.53</v>
       </c>
       <c r="M33">
-        <v>0.5519922</v>
+        <v>0.5697984</v>
       </c>
       <c r="N33">
-        <v>30.9780078</v>
+        <v>30.9602016</v>
       </c>
       <c r="O33">
-        <v>9.29340234</v>
+        <v>9.28806048</v>
       </c>
       <c r="P33">
-        <v>21.68460546</v>
+        <v>21.67214112</v>
       </c>
       <c r="Q33">
-        <v>26.75460546</v>
+        <v>26.74214112</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1167706838662227</v>
+        <v>0.1175761751222438</v>
       </c>
       <c r="T33">
-        <v>1.639045816771888</v>
+        <v>1.657648386195007</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>57.1203723530876</v>
+        <v>55.33536071705361</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4271,22 +4271,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09121899908312578</v>
+        <v>0.09095112629855788</v>
       </c>
       <c r="C34">
-        <v>24.1017632652726</v>
+        <v>23.76438946632581</v>
       </c>
       <c r="D34">
-        <v>31.3897632652726</v>
+        <v>31.40638946632581</v>
       </c>
       <c r="E34">
-        <v>-1.972</v>
+        <v>-1.617999999999999</v>
       </c>
       <c r="F34">
-        <v>11.328</v>
+        <v>11.682</v>
       </c>
       <c r="G34">
         <v>4.04</v>
@@ -4307,28 +4307,28 @@
         <v>31.53</v>
       </c>
       <c r="M34">
-        <v>0.5697984</v>
+        <v>0.5876046</v>
       </c>
       <c r="N34">
-        <v>30.9602016</v>
+        <v>30.9423954</v>
       </c>
       <c r="O34">
-        <v>9.28806048</v>
+        <v>9.282718620000001</v>
       </c>
       <c r="P34">
-        <v>21.67214112</v>
+        <v>21.65967678</v>
       </c>
       <c r="Q34">
-        <v>26.74214112</v>
+        <v>26.72967678</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1175761751222438</v>
+        <v>0.11840571089337</v>
       </c>
       <c r="T34">
-        <v>1.657648386195007</v>
+        <v>1.676806256197922</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>55.33536071705361</v>
+        <v>53.65853160441562</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4353,22 +4353,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09095112629855788</v>
+        <v>0.09068325351398998</v>
       </c>
       <c r="C35">
-        <v>23.76438946632581</v>
+        <v>23.427033289497</v>
       </c>
       <c r="D35">
-        <v>31.40638946632581</v>
+        <v>31.423033289497</v>
       </c>
       <c r="E35">
-        <v>-1.617999999999999</v>
+        <v>-1.263999999999998</v>
       </c>
       <c r="F35">
-        <v>11.682</v>
+        <v>12.036</v>
       </c>
       <c r="G35">
         <v>4.04</v>
@@ -4389,28 +4389,28 @@
         <v>31.53</v>
       </c>
       <c r="M35">
-        <v>0.5876046</v>
+        <v>0.6054108000000001</v>
       </c>
       <c r="N35">
-        <v>30.9423954</v>
+        <v>30.9245892</v>
       </c>
       <c r="O35">
-        <v>9.282718620000001</v>
+        <v>9.277376759999999</v>
       </c>
       <c r="P35">
-        <v>21.65967678</v>
+        <v>21.64721244</v>
       </c>
       <c r="Q35">
-        <v>26.72967678</v>
+        <v>26.71721244</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.11840571089337</v>
+        <v>0.119260384112106</v>
       </c>
       <c r="T35">
-        <v>1.676806256197922</v>
+        <v>1.696544667716075</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>53.65853160441562</v>
+        <v>52.08033949840338</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4435,22 +4435,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09068325351398998</v>
+        <v>0.0904153807294221</v>
       </c>
       <c r="C36">
-        <v>23.427033289497</v>
+        <v>23.08969476281757</v>
       </c>
       <c r="D36">
-        <v>31.423033289497</v>
+        <v>31.43969476281757</v>
       </c>
       <c r="E36">
-        <v>-1.263999999999998</v>
+        <v>-0.9099999999999984</v>
       </c>
       <c r="F36">
-        <v>12.036</v>
+        <v>12.39</v>
       </c>
       <c r="G36">
         <v>4.04</v>
@@ -4471,28 +4471,28 @@
         <v>31.53</v>
       </c>
       <c r="M36">
-        <v>0.6054108000000001</v>
+        <v>0.6232170000000001</v>
       </c>
       <c r="N36">
-        <v>30.9245892</v>
+        <v>30.906783</v>
       </c>
       <c r="O36">
-        <v>9.277376759999999</v>
+        <v>9.2720349</v>
       </c>
       <c r="P36">
-        <v>21.64721244</v>
+        <v>21.6347481</v>
       </c>
       <c r="Q36">
-        <v>26.71721244</v>
+        <v>26.7047481</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.119260384112106</v>
+        <v>0.1201413549683417</v>
       </c>
       <c r="T36">
-        <v>1.696544667716075</v>
+        <v>1.716890414973249</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4509,7 +4509,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>52.08033949840338</v>
+        <v>50.59232979844901</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4517,22 +4517,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0904153807294221</v>
+        <v>0.09014750794485418</v>
       </c>
       <c r="C37">
-        <v>23.08969476281757</v>
+        <v>22.7523739143784</v>
       </c>
       <c r="D37">
-        <v>31.43969476281757</v>
+        <v>31.4563739143784</v>
       </c>
       <c r="E37">
-        <v>-0.9099999999999984</v>
+        <v>-0.5559999999999974</v>
       </c>
       <c r="F37">
-        <v>12.39</v>
+        <v>12.744</v>
       </c>
       <c r="G37">
         <v>4.04</v>
@@ -4553,28 +4553,28 @@
         <v>31.53</v>
       </c>
       <c r="M37">
-        <v>0.6232170000000001</v>
+        <v>0.6410232000000001</v>
       </c>
       <c r="N37">
-        <v>30.906783</v>
+        <v>30.8889768</v>
       </c>
       <c r="O37">
-        <v>9.2720349</v>
+        <v>9.26669304</v>
       </c>
       <c r="P37">
-        <v>21.6347481</v>
+        <v>21.62228376</v>
       </c>
       <c r="Q37">
-        <v>26.7047481</v>
+        <v>26.69228376</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1201413549683417</v>
+        <v>0.1210498561638347</v>
       </c>
       <c r="T37">
-        <v>1.716890414973249</v>
+        <v>1.73787196683221</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>50.59232979844901</v>
+        <v>49.18698730404765</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4599,22 +4599,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0901475079448542</v>
+        <v>0.0898796351602863</v>
       </c>
       <c r="C38">
-        <v>22.7523739143784</v>
+        <v>22.41507077232999</v>
       </c>
       <c r="D38">
-        <v>31.4563739143784</v>
+        <v>31.47307077232999</v>
       </c>
       <c r="E38">
-        <v>-0.5559999999999992</v>
+        <v>-0.2019999999999982</v>
       </c>
       <c r="F38">
-        <v>12.744</v>
+        <v>13.098</v>
       </c>
       <c r="G38">
         <v>4.04</v>
@@ -4635,28 +4635,28 @@
         <v>31.53</v>
       </c>
       <c r="M38">
-        <v>0.6410232</v>
+        <v>0.6588294000000001</v>
       </c>
       <c r="N38">
-        <v>30.8889768</v>
+        <v>30.8711706</v>
       </c>
       <c r="O38">
-        <v>9.26669304</v>
+        <v>9.26135118</v>
       </c>
       <c r="P38">
-        <v>21.62228376</v>
+        <v>21.60981942</v>
       </c>
       <c r="Q38">
-        <v>26.69228376</v>
+        <v>26.67981942</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1210498561638347</v>
+        <v>0.1219871986671211</v>
       </c>
       <c r="T38">
-        <v>1.73787196683221</v>
+        <v>1.759519599702566</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>49.18698730404765</v>
+        <v>47.85760926880311</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0898796351602863</v>
+        <v>0.0896117623757184</v>
       </c>
       <c r="C39">
-        <v>22.41507077232999</v>
+        <v>22.07778536488268</v>
       </c>
       <c r="D39">
-        <v>31.47307077232999</v>
+        <v>31.48978536488267</v>
       </c>
       <c r="E39">
-        <v>-0.2019999999999982</v>
+        <v>0.152000000000001</v>
       </c>
       <c r="F39">
-        <v>13.098</v>
+        <v>13.452</v>
       </c>
       <c r="G39">
         <v>4.04</v>
@@ -4717,28 +4717,28 @@
         <v>31.53</v>
       </c>
       <c r="M39">
-        <v>0.6588294000000001</v>
+        <v>0.6766356</v>
       </c>
       <c r="N39">
-        <v>30.8711706</v>
+        <v>30.8533644</v>
       </c>
       <c r="O39">
-        <v>9.26135118</v>
+        <v>9.25600932</v>
       </c>
       <c r="P39">
-        <v>21.60981942</v>
+        <v>21.59735508</v>
       </c>
       <c r="Q39">
-        <v>26.67981942</v>
+        <v>26.66735508</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1219871986671211</v>
+        <v>0.1229547780253523</v>
       </c>
       <c r="T39">
-        <v>1.759519599702566</v>
+        <v>1.781865543310676</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>47.85760926880311</v>
+        <v>46.59819849857146</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4763,22 +4763,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0896117623757184</v>
+        <v>0.08934388959115051</v>
       </c>
       <c r="C40">
-        <v>22.07778536488268</v>
+        <v>21.74051772030671</v>
       </c>
       <c r="D40">
-        <v>31.48978536488267</v>
+        <v>31.50651772030671</v>
       </c>
       <c r="E40">
-        <v>0.152000000000001</v>
+        <v>0.506000000000002</v>
       </c>
       <c r="F40">
-        <v>13.452</v>
+        <v>13.806</v>
       </c>
       <c r="G40">
         <v>4.04</v>
@@ -4799,28 +4799,28 @@
         <v>31.53</v>
       </c>
       <c r="M40">
-        <v>0.6766356</v>
+        <v>0.6944418000000001</v>
       </c>
       <c r="N40">
-        <v>30.8533644</v>
+        <v>30.8355582</v>
       </c>
       <c r="O40">
-        <v>9.25600932</v>
+        <v>9.250667460000001</v>
       </c>
       <c r="P40">
-        <v>21.59735508</v>
+        <v>21.58489074</v>
       </c>
       <c r="Q40">
-        <v>26.66735508</v>
+        <v>26.65489074</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1229547780253523</v>
+        <v>0.1239540812969681</v>
       </c>
       <c r="T40">
-        <v>1.781865543310676</v>
+        <v>1.804944140807577</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>46.59819849857146</v>
+        <v>45.40337289604398</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4845,22 +4845,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08934388959115051</v>
+        <v>0.08907601680658261</v>
       </c>
       <c r="C41">
-        <v>21.74051772030671</v>
+        <v>21.40326786693252</v>
       </c>
       <c r="D41">
-        <v>31.50651772030671</v>
+        <v>31.52326786693252</v>
       </c>
       <c r="E41">
-        <v>0.506000000000002</v>
+        <v>0.860000000000003</v>
       </c>
       <c r="F41">
-        <v>13.806</v>
+        <v>14.16</v>
       </c>
       <c r="G41">
         <v>4.04</v>
@@ -4881,28 +4881,28 @@
         <v>31.53</v>
       </c>
       <c r="M41">
-        <v>0.6944418000000001</v>
+        <v>0.7122480000000001</v>
       </c>
       <c r="N41">
-        <v>30.8355582</v>
+        <v>30.817752</v>
       </c>
       <c r="O41">
-        <v>9.250667460000001</v>
+        <v>9.245325600000001</v>
       </c>
       <c r="P41">
-        <v>21.58489074</v>
+        <v>21.5724264</v>
       </c>
       <c r="Q41">
-        <v>26.65489074</v>
+        <v>26.6424264</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1239540812969681</v>
+        <v>0.1249866946776377</v>
       </c>
       <c r="T41">
-        <v>1.804944140807577</v>
+        <v>1.828792024887707</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4919,7 +4919,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>45.40337289604398</v>
+        <v>44.26828857364288</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4927,22 +4927,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08907601680658261</v>
+        <v>0.08880814402201473</v>
       </c>
       <c r="C42">
-        <v>21.40326786693252</v>
+        <v>21.06603583315076</v>
       </c>
       <c r="D42">
-        <v>31.52326786693252</v>
+        <v>31.54003583315076</v>
       </c>
       <c r="E42">
-        <v>0.860000000000003</v>
+        <v>1.214000000000002</v>
       </c>
       <c r="F42">
-        <v>14.16</v>
+        <v>14.514</v>
       </c>
       <c r="G42">
         <v>4.04</v>
@@ -4963,28 +4963,28 @@
         <v>31.53</v>
       </c>
       <c r="M42">
-        <v>0.7122480000000001</v>
+        <v>0.7300542000000001</v>
       </c>
       <c r="N42">
-        <v>30.817752</v>
+        <v>30.7999458</v>
       </c>
       <c r="O42">
-        <v>9.245325600000001</v>
+        <v>9.23998374</v>
       </c>
       <c r="P42">
-        <v>21.5724264</v>
+        <v>21.55996206</v>
       </c>
       <c r="Q42">
-        <v>26.6424264</v>
+        <v>26.62996206</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1249866946776377</v>
+        <v>0.1260543119017199</v>
       </c>
       <c r="T42">
-        <v>1.828792024887707</v>
+        <v>1.853448311818011</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>44.26828857364288</v>
+        <v>43.18857421818818</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5009,22 +5009,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08880814402201473</v>
+        <v>0.08854027123744683</v>
       </c>
       <c r="C43">
-        <v>21.06603583315076</v>
+        <v>20.72882164741254</v>
       </c>
       <c r="D43">
-        <v>31.54003583315076</v>
+        <v>31.55682164741254</v>
       </c>
       <c r="E43">
-        <v>1.214000000000002</v>
+        <v>1.568000000000003</v>
       </c>
       <c r="F43">
-        <v>14.514</v>
+        <v>14.868</v>
       </c>
       <c r="G43">
         <v>4.04</v>
@@ -5045,28 +5045,28 @@
         <v>31.53</v>
       </c>
       <c r="M43">
-        <v>0.7300542000000001</v>
+        <v>0.7478604000000002</v>
       </c>
       <c r="N43">
-        <v>30.7999458</v>
+        <v>30.7821396</v>
       </c>
       <c r="O43">
-        <v>9.23998374</v>
+        <v>9.23464188</v>
       </c>
       <c r="P43">
-        <v>21.55996206</v>
+        <v>21.54749772</v>
       </c>
       <c r="Q43">
-        <v>26.62996206</v>
+        <v>26.61749772</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1260543119017199</v>
+        <v>0.1271587435128394</v>
       </c>
       <c r="T43">
-        <v>1.853448311818011</v>
+        <v>1.878954815539016</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>43.18857421818818</v>
+        <v>42.16027483204083</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5091,22 +5091,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08854027123744683</v>
+        <v>0.08827239845287893</v>
       </c>
       <c r="C44">
-        <v>20.72882164741254</v>
+        <v>20.39162533822958</v>
       </c>
       <c r="D44">
-        <v>31.55682164741254</v>
+        <v>31.57362533822958</v>
       </c>
       <c r="E44">
-        <v>1.568000000000001</v>
+        <v>1.922000000000002</v>
       </c>
       <c r="F44">
-        <v>14.868</v>
+        <v>15.222</v>
       </c>
       <c r="G44">
         <v>4.04</v>
@@ -5127,28 +5127,28 @@
         <v>31.53</v>
       </c>
       <c r="M44">
-        <v>0.7478604000000001</v>
+        <v>0.7656666000000001</v>
       </c>
       <c r="N44">
-        <v>30.7821396</v>
+        <v>30.7643334</v>
       </c>
       <c r="O44">
-        <v>9.23464188</v>
+        <v>9.22930002</v>
       </c>
       <c r="P44">
-        <v>21.54749772</v>
+        <v>21.53503338</v>
       </c>
       <c r="Q44">
-        <v>26.61749772</v>
+        <v>26.60503338</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1271587435128393</v>
+        <v>0.1283019271103139</v>
       </c>
       <c r="T44">
-        <v>1.878954815539015</v>
+        <v>1.905356284302862</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>42.16027483204084</v>
+        <v>41.17980332431896</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5173,22 +5173,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08827239845287893</v>
+        <v>0.08800452566831105</v>
       </c>
       <c r="C45">
-        <v>20.39162533822958</v>
+        <v>20.05444693417435</v>
       </c>
       <c r="D45">
-        <v>31.57362533822958</v>
+        <v>31.59044693417435</v>
       </c>
       <c r="E45">
-        <v>1.922000000000002</v>
+        <v>2.276000000000002</v>
       </c>
       <c r="F45">
-        <v>15.222</v>
+        <v>15.576</v>
       </c>
       <c r="G45">
         <v>4.04</v>
@@ -5209,28 +5209,28 @@
         <v>31.53</v>
       </c>
       <c r="M45">
-        <v>0.7656666000000001</v>
+        <v>0.7834728000000001</v>
       </c>
       <c r="N45">
-        <v>30.7643334</v>
+        <v>30.7465272</v>
       </c>
       <c r="O45">
-        <v>9.22930002</v>
+        <v>9.22395816</v>
       </c>
       <c r="P45">
-        <v>21.53503338</v>
+        <v>21.52256904</v>
       </c>
       <c r="Q45">
-        <v>26.60503338</v>
+        <v>26.59256904</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1283019271103139</v>
+        <v>0.1294859386934126</v>
       </c>
       <c r="T45">
-        <v>1.905356284302862</v>
+        <v>1.932700662665418</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>41.17980332431896</v>
+        <v>40.24389870331171</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5255,22 +5255,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08800452566831105</v>
+        <v>0.08773665288374316</v>
       </c>
       <c r="C46">
-        <v>20.05444693417435</v>
+        <v>19.71728646388025</v>
       </c>
       <c r="D46">
-        <v>31.59044693417435</v>
+        <v>31.60728646388025</v>
       </c>
       <c r="E46">
-        <v>2.276000000000002</v>
+        <v>2.630000000000003</v>
       </c>
       <c r="F46">
-        <v>15.576</v>
+        <v>15.93</v>
       </c>
       <c r="G46">
         <v>4.04</v>
@@ -5291,28 +5291,28 @@
         <v>31.53</v>
       </c>
       <c r="M46">
-        <v>0.7834728000000001</v>
+        <v>0.8012790000000001</v>
       </c>
       <c r="N46">
-        <v>30.7465272</v>
+        <v>30.728721</v>
       </c>
       <c r="O46">
-        <v>9.22395816</v>
+        <v>9.218616299999999</v>
       </c>
       <c r="P46">
-        <v>21.52256904</v>
+        <v>21.5101047</v>
       </c>
       <c r="Q46">
-        <v>26.59256904</v>
+        <v>26.5801047</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1294859386934126</v>
+        <v>0.1307130052431694</v>
       </c>
       <c r="T46">
-        <v>1.932700662665418</v>
+        <v>1.961039382059339</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>40.24389870331171</v>
+        <v>39.34958984323812</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5337,22 +5337,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08773665288374316</v>
+        <v>0.08746878009917525</v>
       </c>
       <c r="C47">
-        <v>19.71728646388025</v>
+        <v>19.38014395604176</v>
       </c>
       <c r="D47">
-        <v>31.60728646388025</v>
+        <v>31.62414395604176</v>
       </c>
       <c r="E47">
-        <v>2.630000000000003</v>
+        <v>2.984000000000002</v>
       </c>
       <c r="F47">
-        <v>15.93</v>
+        <v>16.284</v>
       </c>
       <c r="G47">
         <v>4.04</v>
@@ -5373,28 +5373,28 @@
         <v>31.53</v>
       </c>
       <c r="M47">
-        <v>0.8012790000000001</v>
+        <v>0.8190852000000001</v>
       </c>
       <c r="N47">
-        <v>30.728721</v>
+        <v>30.7109148</v>
       </c>
       <c r="O47">
-        <v>9.218616299999999</v>
+        <v>9.213274439999999</v>
       </c>
       <c r="P47">
-        <v>21.5101047</v>
+        <v>21.49764036</v>
       </c>
       <c r="Q47">
-        <v>26.5801047</v>
+        <v>26.56764036</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1307130052431694</v>
+        <v>0.1319855187021764</v>
       </c>
       <c r="T47">
-        <v>1.961039382059339</v>
+        <v>1.990427683653034</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>39.34958984323812</v>
+        <v>38.49416397708077</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5419,22 +5419,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08746878009917525</v>
+        <v>0.08720090731460736</v>
       </c>
       <c r="C48">
-        <v>19.38014395604176</v>
+        <v>19.0430194394146</v>
       </c>
       <c r="D48">
-        <v>31.62414395604176</v>
+        <v>31.64101943941461</v>
       </c>
       <c r="E48">
-        <v>2.984000000000002</v>
+        <v>3.338000000000005</v>
       </c>
       <c r="F48">
-        <v>16.284</v>
+        <v>16.63800000000001</v>
       </c>
       <c r="G48">
         <v>4.04</v>
@@ -5455,28 +5455,28 @@
         <v>31.53</v>
       </c>
       <c r="M48">
-        <v>0.8190852000000001</v>
+        <v>0.8368914000000002</v>
       </c>
       <c r="N48">
-        <v>30.7109148</v>
+        <v>30.6931086</v>
       </c>
       <c r="O48">
-        <v>9.213274439999999</v>
+        <v>9.20793258</v>
       </c>
       <c r="P48">
-        <v>21.49764036</v>
+        <v>21.48517602</v>
       </c>
       <c r="Q48">
-        <v>26.56764036</v>
+        <v>26.55517602</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1319855187021764</v>
+        <v>0.133306051536995</v>
       </c>
       <c r="T48">
-        <v>1.990427683653034</v>
+        <v>2.0209249777597</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5493,7 +5493,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>38.49416397708077</v>
+        <v>37.67513921161096</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5501,22 +5501,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08720090731460736</v>
+        <v>0.08693303453003948</v>
       </c>
       <c r="C49">
-        <v>19.0430194394146</v>
+        <v>18.70591294281594</v>
       </c>
       <c r="D49">
-        <v>31.64101943941461</v>
+        <v>31.65791294281594</v>
       </c>
       <c r="E49">
-        <v>3.338000000000005</v>
+        <v>3.692000000000004</v>
       </c>
       <c r="F49">
-        <v>16.63800000000001</v>
+        <v>16.992</v>
       </c>
       <c r="G49">
         <v>4.04</v>
@@ -5537,28 +5537,28 @@
         <v>31.53</v>
       </c>
       <c r="M49">
-        <v>0.8368914000000002</v>
+        <v>0.8546976000000002</v>
       </c>
       <c r="N49">
-        <v>30.6931086</v>
+        <v>30.6753024</v>
       </c>
       <c r="O49">
-        <v>9.20793258</v>
+        <v>9.20259072</v>
       </c>
       <c r="P49">
-        <v>21.48517602</v>
+        <v>21.47271168</v>
       </c>
       <c r="Q49">
-        <v>26.55517602</v>
+        <v>26.54271168</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.133306051536995</v>
+        <v>0.1346773740962297</v>
       </c>
       <c r="T49">
-        <v>2.0209249777597</v>
+        <v>2.052595244716622</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>37.67513921161096</v>
+        <v>36.89024047803574</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5583,22 +5583,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08693303453003946</v>
+        <v>0.08666516174547155</v>
       </c>
       <c r="C50">
-        <v>18.70591294281594</v>
+        <v>18.36882449512447</v>
       </c>
       <c r="D50">
-        <v>31.65791294281594</v>
+        <v>31.67482449512447</v>
       </c>
       <c r="E50">
-        <v>3.692</v>
+        <v>4.046000000000003</v>
       </c>
       <c r="F50">
-        <v>16.992</v>
+        <v>17.346</v>
       </c>
       <c r="G50">
         <v>4.04</v>
@@ -5619,28 +5619,28 @@
         <v>31.53</v>
       </c>
       <c r="M50">
-        <v>0.8546975999999999</v>
+        <v>0.8725038000000002</v>
       </c>
       <c r="N50">
-        <v>30.6753024</v>
+        <v>30.6574962</v>
       </c>
       <c r="O50">
-        <v>9.20259072</v>
+        <v>9.19724886</v>
       </c>
       <c r="P50">
-        <v>21.47271168</v>
+        <v>21.46024734</v>
       </c>
       <c r="Q50">
-        <v>26.54271168</v>
+        <v>26.53024734</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1346773740962297</v>
+        <v>0.1361024740107285</v>
       </c>
       <c r="T50">
-        <v>2.052595244716622</v>
+        <v>2.085507482926757</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>36.89024047803574</v>
+        <v>36.13737842746357</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5665,22 +5665,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08666516174547155</v>
+        <v>0.08639728896090366</v>
       </c>
       <c r="C51">
-        <v>18.36882449512447</v>
+        <v>18.03175412528066</v>
       </c>
       <c r="D51">
-        <v>31.67482449512447</v>
+        <v>31.69175412528066</v>
       </c>
       <c r="E51">
-        <v>4.046000000000003</v>
+        <v>4.400000000000002</v>
       </c>
       <c r="F51">
-        <v>17.346</v>
+        <v>17.7</v>
       </c>
       <c r="G51">
         <v>4.04</v>
@@ -5701,28 +5701,28 @@
         <v>31.53</v>
       </c>
       <c r="M51">
-        <v>0.8725038000000002</v>
+        <v>0.89031</v>
       </c>
       <c r="N51">
-        <v>30.6574962</v>
+        <v>30.63969</v>
       </c>
       <c r="O51">
-        <v>9.19724886</v>
+        <v>9.191907</v>
       </c>
       <c r="P51">
-        <v>21.46024734</v>
+        <v>21.447783</v>
       </c>
       <c r="Q51">
-        <v>26.53024734</v>
+        <v>26.517783</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1361024740107285</v>
+        <v>0.1375845779218073</v>
       </c>
       <c r="T51">
-        <v>2.085507482926757</v>
+        <v>2.119736210665297</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>36.13737842746357</v>
+        <v>35.41463085891431</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08639728896090366</v>
+        <v>0.08612941617633578</v>
       </c>
       <c r="C52">
-        <v>18.03175412528066</v>
+        <v>17.69470186228688</v>
       </c>
       <c r="D52">
-        <v>31.69175412528066</v>
+        <v>31.70870186228688</v>
       </c>
       <c r="E52">
-        <v>4.400000000000002</v>
+        <v>4.754000000000001</v>
       </c>
       <c r="F52">
-        <v>17.7</v>
+        <v>18.054</v>
       </c>
       <c r="G52">
         <v>4.04</v>
@@ -5783,28 +5783,28 @@
         <v>31.53</v>
       </c>
       <c r="M52">
-        <v>0.89031</v>
+        <v>0.9081162</v>
       </c>
       <c r="N52">
-        <v>30.63969</v>
+        <v>30.6218838</v>
       </c>
       <c r="O52">
-        <v>9.191907</v>
+        <v>9.186565140000001</v>
       </c>
       <c r="P52">
-        <v>21.447783</v>
+        <v>21.43531866</v>
       </c>
       <c r="Q52">
-        <v>26.517783</v>
+        <v>26.50531866</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1375845779218073</v>
+        <v>0.139127175870073</v>
       </c>
       <c r="T52">
-        <v>2.119736210665297</v>
+        <v>2.155362029331941</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5821,7 +5821,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>35.41463085891431</v>
+        <v>34.72022633226894</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5829,22 +5829,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08612941617633578</v>
+        <v>0.08586154339176787</v>
       </c>
       <c r="C53">
-        <v>17.69470186228688</v>
+        <v>17.35766773520756</v>
       </c>
       <c r="D53">
-        <v>31.70870186228688</v>
+        <v>31.72566773520756</v>
       </c>
       <c r="E53">
-        <v>4.754000000000001</v>
+        <v>5.108000000000004</v>
       </c>
       <c r="F53">
-        <v>18.054</v>
+        <v>18.408</v>
       </c>
       <c r="G53">
         <v>4.04</v>
@@ -5865,28 +5865,28 @@
         <v>31.53</v>
       </c>
       <c r="M53">
-        <v>0.9081162</v>
+        <v>0.9259224000000001</v>
       </c>
       <c r="N53">
-        <v>30.6218838</v>
+        <v>30.6040776</v>
       </c>
       <c r="O53">
-        <v>9.186565140000001</v>
+        <v>9.181223279999999</v>
       </c>
       <c r="P53">
-        <v>21.43531866</v>
+        <v>21.42285432</v>
       </c>
       <c r="Q53">
-        <v>26.50531866</v>
+        <v>26.49285432</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.139127175870073</v>
+        <v>0.1407340487328497</v>
       </c>
       <c r="T53">
-        <v>2.155362029331941</v>
+        <v>2.192472257109694</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>34.72022633226894</v>
+        <v>34.05252967203299</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5911,22 +5911,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08586154339176787</v>
+        <v>0.08559367060719997</v>
       </c>
       <c r="C54">
-        <v>17.35766773520756</v>
+        <v>17.02065177316937</v>
       </c>
       <c r="D54">
-        <v>31.72566773520756</v>
+        <v>31.74265177316937</v>
       </c>
       <c r="E54">
-        <v>5.108000000000004</v>
+        <v>5.462000000000003</v>
       </c>
       <c r="F54">
-        <v>18.408</v>
+        <v>18.762</v>
       </c>
       <c r="G54">
         <v>4.04</v>
@@ -5947,28 +5947,28 @@
         <v>31.53</v>
       </c>
       <c r="M54">
-        <v>0.9259224000000001</v>
+        <v>0.9437286000000001</v>
       </c>
       <c r="N54">
-        <v>30.6040776</v>
+        <v>30.5862714</v>
       </c>
       <c r="O54">
-        <v>9.181223279999999</v>
+        <v>9.17588142</v>
       </c>
       <c r="P54">
-        <v>21.42285432</v>
+        <v>21.41038998</v>
       </c>
       <c r="Q54">
-        <v>26.49285432</v>
+        <v>26.48038998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1407340487328497</v>
+        <v>0.1424092991642553</v>
       </c>
       <c r="T54">
-        <v>2.192472257109694</v>
+        <v>2.231161643516288</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>34.05252967203299</v>
+        <v>33.41002911218331</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5993,22 +5993,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08559367060719997</v>
+        <v>0.08532579782263207</v>
       </c>
       <c r="C55">
-        <v>17.02065177316937</v>
+        <v>16.68365400536141</v>
       </c>
       <c r="D55">
-        <v>31.74265177316937</v>
+        <v>31.75965400536141</v>
       </c>
       <c r="E55">
-        <v>5.462000000000003</v>
+        <v>5.816000000000003</v>
       </c>
       <c r="F55">
-        <v>18.762</v>
+        <v>19.116</v>
       </c>
       <c r="G55">
         <v>4.04</v>
@@ -6029,28 +6029,28 @@
         <v>31.53</v>
       </c>
       <c r="M55">
-        <v>0.9437286000000001</v>
+        <v>0.9615348000000001</v>
       </c>
       <c r="N55">
-        <v>30.5862714</v>
+        <v>30.5684652</v>
       </c>
       <c r="O55">
-        <v>9.17588142</v>
+        <v>9.17053956</v>
       </c>
       <c r="P55">
-        <v>21.41038998</v>
+        <v>21.39792564</v>
       </c>
       <c r="Q55">
-        <v>26.48038998</v>
+        <v>26.46792564</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1424092991642553</v>
+        <v>0.1441573865709393</v>
       </c>
       <c r="T55">
-        <v>2.231161643516288</v>
+        <v>2.271533177157952</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>33.41002911218331</v>
+        <v>32.7913248693651</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6075,22 +6075,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08532579782263207</v>
+        <v>0.0850579250380642</v>
       </c>
       <c r="C56">
-        <v>16.68365400536141</v>
+        <v>16.3466744610353</v>
       </c>
       <c r="D56">
-        <v>31.75965400536141</v>
+        <v>31.7766744610353</v>
       </c>
       <c r="E56">
-        <v>5.816000000000003</v>
+        <v>6.170000000000005</v>
       </c>
       <c r="F56">
-        <v>19.116</v>
+        <v>19.47000000000001</v>
       </c>
       <c r="G56">
         <v>4.04</v>
@@ -6111,28 +6111,28 @@
         <v>31.53</v>
       </c>
       <c r="M56">
-        <v>0.9615348000000001</v>
+        <v>0.9793410000000002</v>
       </c>
       <c r="N56">
-        <v>30.5684652</v>
+        <v>30.550659</v>
       </c>
       <c r="O56">
-        <v>9.17053956</v>
+        <v>9.1651977</v>
       </c>
       <c r="P56">
-        <v>21.39792564</v>
+        <v>21.3854613</v>
       </c>
       <c r="Q56">
-        <v>26.46792564</v>
+        <v>26.4554613</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1441573865709393</v>
+        <v>0.1459831667512538</v>
       </c>
       <c r="T56">
-        <v>2.271533177157952</v>
+        <v>2.31369900118369</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>32.7913248693651</v>
+        <v>32.19511896264936</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6157,22 +6157,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0850579250380642</v>
+        <v>0.08479005225349628</v>
       </c>
       <c r="C57">
-        <v>16.3466744610353</v>
+        <v>16.00971316950545</v>
       </c>
       <c r="D57">
-        <v>31.7766744610353</v>
+        <v>31.79371316950545</v>
       </c>
       <c r="E57">
-        <v>6.170000000000005</v>
+        <v>6.524000000000004</v>
       </c>
       <c r="F57">
-        <v>19.47000000000001</v>
+        <v>19.82400000000001</v>
       </c>
       <c r="G57">
         <v>4.04</v>
@@ -6193,28 +6193,28 @@
         <v>31.53</v>
       </c>
       <c r="M57">
-        <v>0.9793410000000002</v>
+        <v>0.9971472000000002</v>
       </c>
       <c r="N57">
-        <v>30.550659</v>
+        <v>30.5328528</v>
       </c>
       <c r="O57">
-        <v>9.1651977</v>
+        <v>9.159855840000001</v>
       </c>
       <c r="P57">
-        <v>21.3854613</v>
+        <v>21.37299696</v>
       </c>
       <c r="Q57">
-        <v>26.4554613</v>
+        <v>26.44299696</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1459831667512538</v>
+        <v>0.1478919369397643</v>
       </c>
       <c r="T57">
-        <v>2.31369900118369</v>
+        <v>2.357781453574234</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>32.19511896264936</v>
+        <v>31.62020612403063</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6239,22 +6239,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08479005225349628</v>
+        <v>0.0845221794689284</v>
       </c>
       <c r="C58">
-        <v>16.00971316950545</v>
+        <v>15.67277016014914</v>
       </c>
       <c r="D58">
-        <v>31.79371316950545</v>
+        <v>31.81077016014915</v>
       </c>
       <c r="E58">
-        <v>6.524000000000004</v>
+        <v>6.878000000000004</v>
       </c>
       <c r="F58">
-        <v>19.82400000000001</v>
+        <v>20.178</v>
       </c>
       <c r="G58">
         <v>4.04</v>
@@ -6275,28 +6275,28 @@
         <v>31.53</v>
       </c>
       <c r="M58">
-        <v>0.9971472000000002</v>
+        <v>1.0149534</v>
       </c>
       <c r="N58">
-        <v>30.5328528</v>
+        <v>30.5150466</v>
       </c>
       <c r="O58">
-        <v>9.159855840000001</v>
+        <v>9.154513980000001</v>
       </c>
       <c r="P58">
-        <v>21.37299696</v>
+        <v>21.36053262</v>
       </c>
       <c r="Q58">
-        <v>26.44299696</v>
+        <v>26.43053262</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1478919369397643</v>
+        <v>0.1498894871370428</v>
       </c>
       <c r="T58">
-        <v>2.357781453574234</v>
+        <v>2.403914252587594</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6313,7 +6313,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>31.62020612403063</v>
+        <v>31.0654656657143</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6321,22 +6321,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0845221794689284</v>
+        <v>0.0842543066843605</v>
       </c>
       <c r="C59">
-        <v>15.67277016014914</v>
+        <v>15.33584546240675</v>
       </c>
       <c r="D59">
-        <v>31.81077016014915</v>
+        <v>31.82784546240676</v>
       </c>
       <c r="E59">
-        <v>6.878000000000004</v>
+        <v>7.232000000000006</v>
       </c>
       <c r="F59">
-        <v>20.178</v>
+        <v>20.53200000000001</v>
       </c>
       <c r="G59">
         <v>4.04</v>
@@ -6357,28 +6357,28 @@
         <v>31.53</v>
       </c>
       <c r="M59">
-        <v>1.0149534</v>
+        <v>1.0327596</v>
       </c>
       <c r="N59">
-        <v>30.5150466</v>
+        <v>30.4972404</v>
       </c>
       <c r="O59">
-        <v>9.154513980000001</v>
+        <v>9.149172120000001</v>
       </c>
       <c r="P59">
-        <v>21.36053262</v>
+        <v>21.34806828</v>
       </c>
       <c r="Q59">
-        <v>26.43053262</v>
+        <v>26.41806828</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1498894871370428</v>
+        <v>0.1519821587722869</v>
       </c>
       <c r="T59">
-        <v>2.403914252587594</v>
+        <v>2.452243851553971</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6395,7 +6395,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>31.0654656657143</v>
+        <v>30.52985418871923</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6403,22 +6403,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08425430668436049</v>
+        <v>0.0839864338997926</v>
       </c>
       <c r="C60">
-        <v>15.33584546240676</v>
+        <v>14.99893910578191</v>
       </c>
       <c r="D60">
-        <v>31.82784546240676</v>
+        <v>31.84493910578191</v>
       </c>
       <c r="E60">
-        <v>7.232000000000003</v>
+        <v>7.586000000000002</v>
       </c>
       <c r="F60">
-        <v>20.532</v>
+        <v>20.886</v>
       </c>
       <c r="G60">
         <v>4.04</v>
@@ -6439,28 +6439,28 @@
         <v>31.53</v>
       </c>
       <c r="M60">
-        <v>1.0327596</v>
+        <v>1.0505658</v>
       </c>
       <c r="N60">
-        <v>30.4972404</v>
+        <v>30.4794342</v>
       </c>
       <c r="O60">
-        <v>9.149172120000001</v>
+        <v>9.14383026</v>
       </c>
       <c r="P60">
-        <v>21.34806828</v>
+        <v>21.33560394</v>
       </c>
       <c r="Q60">
-        <v>26.41806828</v>
+        <v>26.40560394</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1519821587722869</v>
+        <v>0.1541769119507136</v>
       </c>
       <c r="T60">
-        <v>2.45224385155397</v>
+        <v>2.502930991933341</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>30.52985418871923</v>
+        <v>30.01239903297823</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6485,22 +6485,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0839864338997926</v>
+        <v>0.08371856111522472</v>
       </c>
       <c r="C61">
-        <v>14.99893910578191</v>
+        <v>14.66205111984164</v>
       </c>
       <c r="D61">
-        <v>31.84493910578191</v>
+        <v>31.86205111984165</v>
       </c>
       <c r="E61">
-        <v>7.586000000000002</v>
+        <v>7.940000000000001</v>
       </c>
       <c r="F61">
-        <v>20.886</v>
+        <v>21.24</v>
       </c>
       <c r="G61">
         <v>4.04</v>
@@ -6521,28 +6521,28 @@
         <v>31.53</v>
       </c>
       <c r="M61">
-        <v>1.0505658</v>
+        <v>1.068372</v>
       </c>
       <c r="N61">
-        <v>30.4794342</v>
+        <v>30.461628</v>
       </c>
       <c r="O61">
-        <v>9.14383026</v>
+        <v>9.1384884</v>
       </c>
       <c r="P61">
-        <v>21.33560394</v>
+        <v>21.3231396</v>
       </c>
       <c r="Q61">
-        <v>26.40560394</v>
+        <v>26.3931396</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1541769119507136</v>
+        <v>0.1564814027880618</v>
       </c>
       <c r="T61">
-        <v>2.502930991933341</v>
+        <v>2.556152489331681</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>30.01239903297823</v>
+        <v>29.51219238242859</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6567,22 +6567,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08371856111522472</v>
+        <v>0.08345068833065682</v>
       </c>
       <c r="C62">
-        <v>14.66205111984164</v>
+        <v>14.32518153421656</v>
       </c>
       <c r="D62">
-        <v>31.86205111984165</v>
+        <v>31.87918153421656</v>
       </c>
       <c r="E62">
-        <v>7.940000000000001</v>
+        <v>8.294000000000004</v>
       </c>
       <c r="F62">
-        <v>21.24</v>
+        <v>21.594</v>
       </c>
       <c r="G62">
         <v>4.04</v>
@@ -6603,28 +6603,28 @@
         <v>31.53</v>
       </c>
       <c r="M62">
-        <v>1.068372</v>
+        <v>1.0861782</v>
       </c>
       <c r="N62">
-        <v>30.461628</v>
+        <v>30.4438218</v>
       </c>
       <c r="O62">
-        <v>9.1384884</v>
+        <v>9.13314654</v>
       </c>
       <c r="P62">
-        <v>21.3231396</v>
+        <v>21.31067526</v>
       </c>
       <c r="Q62">
-        <v>26.3931396</v>
+        <v>26.38067526</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1564814027880618</v>
+        <v>0.1589040726427098</v>
       </c>
       <c r="T62">
-        <v>2.556152489331681</v>
+        <v>2.61210329428891</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>29.51219238242859</v>
+        <v>29.02838594992976</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6649,22 +6649,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08345068833065682</v>
+        <v>0.08318281554608892</v>
       </c>
       <c r="C63">
-        <v>14.32518153421656</v>
+        <v>13.98833037860105</v>
       </c>
       <c r="D63">
-        <v>31.87918153421656</v>
+        <v>31.89633037860105</v>
       </c>
       <c r="E63">
-        <v>8.294000000000004</v>
+        <v>8.648000000000003</v>
       </c>
       <c r="F63">
-        <v>21.594</v>
+        <v>21.948</v>
       </c>
       <c r="G63">
         <v>4.04</v>
@@ -6685,28 +6685,28 @@
         <v>31.53</v>
       </c>
       <c r="M63">
-        <v>1.0861782</v>
+        <v>1.1039844</v>
       </c>
       <c r="N63">
-        <v>30.4438218</v>
+        <v>30.4260156</v>
       </c>
       <c r="O63">
-        <v>9.13314654</v>
+        <v>9.127804679999999</v>
       </c>
       <c r="P63">
-        <v>21.31067526</v>
+        <v>21.29821092</v>
       </c>
       <c r="Q63">
-        <v>26.38067526</v>
+        <v>26.36821092</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1589040726427098</v>
+        <v>0.1614542514370761</v>
       </c>
       <c r="T63">
-        <v>2.61210329428891</v>
+        <v>2.670998878454414</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6723,7 +6723,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>29.02838594992976</v>
+        <v>28.5601861765438</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6731,22 +6731,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08318281554608892</v>
+        <v>0.08291494276152102</v>
       </c>
       <c r="C64">
-        <v>13.98833037860105</v>
+        <v>13.6514976827534</v>
       </c>
       <c r="D64">
-        <v>31.89633037860105</v>
+        <v>31.91349768275341</v>
       </c>
       <c r="E64">
-        <v>8.648000000000003</v>
+        <v>9.002000000000002</v>
       </c>
       <c r="F64">
-        <v>21.948</v>
+        <v>22.302</v>
       </c>
       <c r="G64">
         <v>4.04</v>
@@ -6767,28 +6767,28 @@
         <v>31.53</v>
       </c>
       <c r="M64">
-        <v>1.1039844</v>
+        <v>1.1217906</v>
       </c>
       <c r="N64">
-        <v>30.4260156</v>
+        <v>30.4082094</v>
       </c>
       <c r="O64">
-        <v>9.127804679999999</v>
+        <v>9.122462819999999</v>
       </c>
       <c r="P64">
-        <v>21.29821092</v>
+        <v>21.28574658</v>
       </c>
       <c r="Q64">
-        <v>26.36821092</v>
+        <v>26.35574658</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1614542514370761</v>
+        <v>0.1641422777338406</v>
       </c>
       <c r="T64">
-        <v>2.670998878454414</v>
+        <v>2.733078007709945</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>28.5601861765438</v>
+        <v>28.10684988802723</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08291494276152102</v>
+        <v>0.08264706997695313</v>
       </c>
       <c r="C65">
-        <v>13.6514976827534</v>
+        <v>13.31468347649605</v>
       </c>
       <c r="D65">
-        <v>31.91349768275341</v>
+        <v>31.93068347649605</v>
       </c>
       <c r="E65">
-        <v>9.002000000000002</v>
+        <v>9.356000000000002</v>
       </c>
       <c r="F65">
-        <v>22.302</v>
+        <v>22.656</v>
       </c>
       <c r="G65">
         <v>4.04</v>
@@ -6849,28 +6849,28 @@
         <v>31.53</v>
       </c>
       <c r="M65">
-        <v>1.1217906</v>
+        <v>1.1395968</v>
       </c>
       <c r="N65">
-        <v>30.4082094</v>
+        <v>30.3904032</v>
       </c>
       <c r="O65">
-        <v>9.122462819999999</v>
+        <v>9.117120959999999</v>
       </c>
       <c r="P65">
-        <v>21.28574658</v>
+        <v>21.27328224</v>
       </c>
       <c r="Q65">
-        <v>26.35574658</v>
+        <v>26.34328224</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1641422777338406</v>
+        <v>0.1669796388248698</v>
       </c>
       <c r="T65">
-        <v>2.733078007709945</v>
+        <v>2.798605977479673</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6887,7 +6887,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>28.10684988802723</v>
+        <v>27.66768035852681</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6895,22 +6895,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08264706997695313</v>
+        <v>0.08237919719238523</v>
       </c>
       <c r="C66">
-        <v>13.31468347649605</v>
+        <v>12.97788778971564</v>
       </c>
       <c r="D66">
-        <v>31.93068347649605</v>
+        <v>31.94788778971565</v>
       </c>
       <c r="E66">
-        <v>9.356000000000002</v>
+        <v>9.710000000000004</v>
       </c>
       <c r="F66">
-        <v>22.656</v>
+        <v>23.01000000000001</v>
       </c>
       <c r="G66">
         <v>4.04</v>
@@ -6931,28 +6931,28 @@
         <v>31.53</v>
       </c>
       <c r="M66">
-        <v>1.1395968</v>
+        <v>1.157403</v>
       </c>
       <c r="N66">
-        <v>30.3904032</v>
+        <v>30.372597</v>
       </c>
       <c r="O66">
-        <v>9.117120959999999</v>
+        <v>9.1117791</v>
       </c>
       <c r="P66">
-        <v>21.27328224</v>
+        <v>21.2608179</v>
       </c>
       <c r="Q66">
-        <v>26.34328224</v>
+        <v>26.3308179</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1669796388248698</v>
+        <v>0.1699791348353864</v>
       </c>
       <c r="T66">
-        <v>2.798605977479673</v>
+        <v>2.867878402664813</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>27.66768035852681</v>
+        <v>27.24202373762639</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6977,22 +6977,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08237919719238523</v>
+        <v>0.08211132440781733</v>
       </c>
       <c r="C67">
-        <v>12.97788778971564</v>
+        <v>12.64111065236334</v>
       </c>
       <c r="D67">
-        <v>31.94788778971565</v>
+        <v>31.96511065236334</v>
       </c>
       <c r="E67">
-        <v>9.710000000000004</v>
+        <v>10.064</v>
       </c>
       <c r="F67">
-        <v>23.01000000000001</v>
+        <v>23.364</v>
       </c>
       <c r="G67">
         <v>4.04</v>
@@ -7013,28 +7013,28 @@
         <v>31.53</v>
       </c>
       <c r="M67">
-        <v>1.157403</v>
+        <v>1.1752092</v>
       </c>
       <c r="N67">
-        <v>30.372597</v>
+        <v>30.3547908</v>
       </c>
       <c r="O67">
-        <v>9.1117791</v>
+        <v>9.10643724</v>
       </c>
       <c r="P67">
-        <v>21.2608179</v>
+        <v>21.24835356</v>
       </c>
       <c r="Q67">
-        <v>26.3308179</v>
+        <v>26.31835356</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1699791348353864</v>
+        <v>0.1731550717876981</v>
       </c>
       <c r="T67">
-        <v>2.867878402664813</v>
+        <v>2.941225676390256</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>27.24202373762639</v>
+        <v>26.82926580220781</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7059,22 +7059,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08211132440781733</v>
+        <v>0.08184345162324944</v>
       </c>
       <c r="C68">
-        <v>12.64111065236334</v>
+        <v>12.30435209445486</v>
       </c>
       <c r="D68">
-        <v>31.96511065236334</v>
+        <v>31.98235209445486</v>
       </c>
       <c r="E68">
-        <v>10.064</v>
+        <v>10.418</v>
       </c>
       <c r="F68">
-        <v>23.364</v>
+        <v>23.718</v>
       </c>
       <c r="G68">
         <v>4.04</v>
@@ -7095,28 +7095,28 @@
         <v>31.53</v>
       </c>
       <c r="M68">
-        <v>1.1752092</v>
+        <v>1.1930154</v>
       </c>
       <c r="N68">
-        <v>30.3547908</v>
+        <v>30.3369846</v>
       </c>
       <c r="O68">
-        <v>9.10643724</v>
+        <v>9.10109538</v>
       </c>
       <c r="P68">
-        <v>21.24835356</v>
+        <v>21.23588922</v>
       </c>
       <c r="Q68">
-        <v>26.31835356</v>
+        <v>26.30588922</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1731550717876981</v>
+        <v>0.1765234897674226</v>
       </c>
       <c r="T68">
-        <v>2.941225676390256</v>
+        <v>3.019018239432393</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -7133,7 +7133,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>26.82926580220781</v>
+        <v>26.42882899918978</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7141,22 +7141,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08184345162324944</v>
+        <v>0.08157557883868155</v>
       </c>
       <c r="C69">
-        <v>12.30435209445486</v>
+        <v>11.96761214607075</v>
       </c>
       <c r="D69">
-        <v>31.98235209445486</v>
+        <v>31.99961214607075</v>
       </c>
       <c r="E69">
-        <v>10.418</v>
+        <v>10.77200000000001</v>
       </c>
       <c r="F69">
-        <v>23.718</v>
+        <v>24.07200000000001</v>
       </c>
       <c r="G69">
         <v>4.04</v>
@@ -7177,28 +7177,28 @@
         <v>31.53</v>
       </c>
       <c r="M69">
-        <v>1.1930154</v>
+        <v>1.2108216</v>
       </c>
       <c r="N69">
-        <v>30.3369846</v>
+        <v>30.3191784</v>
       </c>
       <c r="O69">
-        <v>9.10109538</v>
+        <v>9.095753520000001</v>
       </c>
       <c r="P69">
-        <v>21.23588922</v>
+        <v>21.22342488</v>
       </c>
       <c r="Q69">
-        <v>26.30588922</v>
+        <v>26.29342488</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1765234897674226</v>
+        <v>0.1801024338708798</v>
       </c>
       <c r="T69">
-        <v>3.019018239432393</v>
+        <v>3.101672837664662</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -7215,7 +7215,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>26.42882899918978</v>
+        <v>26.0401697492017</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7223,22 +7223,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08157557883868155</v>
+        <v>0.08130770605411365</v>
       </c>
       <c r="C70">
-        <v>11.96761214607075</v>
+        <v>11.63089083735653</v>
       </c>
       <c r="D70">
-        <v>31.99961214607075</v>
+        <v>32.01689083735653</v>
       </c>
       <c r="E70">
-        <v>10.77200000000001</v>
+        <v>11.126</v>
       </c>
       <c r="F70">
-        <v>24.07200000000001</v>
+        <v>24.42600000000001</v>
       </c>
       <c r="G70">
         <v>4.04</v>
@@ -7259,28 +7259,28 @@
         <v>31.53</v>
       </c>
       <c r="M70">
-        <v>1.2108216</v>
+        <v>1.2286278</v>
       </c>
       <c r="N70">
-        <v>30.3191784</v>
+        <v>30.3013722</v>
       </c>
       <c r="O70">
-        <v>9.095753520000001</v>
+        <v>9.090411659999999</v>
       </c>
       <c r="P70">
-        <v>21.22342488</v>
+        <v>21.21096054</v>
       </c>
       <c r="Q70">
-        <v>26.29342488</v>
+        <v>26.28096054</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1801024338708798</v>
+        <v>0.183912277593915</v>
       </c>
       <c r="T70">
-        <v>3.101672837664662</v>
+        <v>3.189659990621595</v>
       </c>
       <c r="U70">
         <v>0.0503</v>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>26.0401697492017</v>
+        <v>25.66277598472051</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7305,22 +7305,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08130770605411365</v>
+        <v>0.08103983326954575</v>
       </c>
       <c r="C71">
-        <v>11.63089083735653</v>
+        <v>11.29418819852286</v>
       </c>
       <c r="D71">
-        <v>32.01689083735653</v>
+        <v>32.03418819852286</v>
       </c>
       <c r="E71">
-        <v>11.126</v>
+        <v>11.48</v>
       </c>
       <c r="F71">
-        <v>24.42600000000001</v>
+        <v>24.78</v>
       </c>
       <c r="G71">
         <v>4.04</v>
@@ -7341,28 +7341,28 @@
         <v>31.53</v>
       </c>
       <c r="M71">
-        <v>1.2286278</v>
+        <v>1.246434</v>
       </c>
       <c r="N71">
-        <v>30.3013722</v>
+        <v>30.283566</v>
       </c>
       <c r="O71">
-        <v>9.090411659999999</v>
+        <v>9.085069799999999</v>
       </c>
       <c r="P71">
-        <v>21.21096054</v>
+        <v>21.1984962</v>
       </c>
       <c r="Q71">
-        <v>26.28096054</v>
+        <v>26.2684962</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.183912277593915</v>
+        <v>0.1879761108984859</v>
       </c>
       <c r="T71">
-        <v>3.189659990621595</v>
+        <v>3.283512953775656</v>
       </c>
       <c r="U71">
         <v>0.0503</v>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>25.66277598472051</v>
+        <v>25.2961648992245</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7387,22 +7387,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08103983326954575</v>
+        <v>0.08077196048497787</v>
       </c>
       <c r="C72">
-        <v>11.29418819852286</v>
+        <v>10.95750425984569</v>
       </c>
       <c r="D72">
-        <v>32.03418819852286</v>
+        <v>32.0515042598457</v>
       </c>
       <c r="E72">
-        <v>11.48</v>
+        <v>11.83400000000001</v>
       </c>
       <c r="F72">
-        <v>24.78</v>
+        <v>25.13400000000001</v>
       </c>
       <c r="G72">
         <v>4.04</v>
@@ -7423,28 +7423,28 @@
         <v>31.53</v>
       </c>
       <c r="M72">
-        <v>1.246434</v>
+        <v>1.2642402</v>
       </c>
       <c r="N72">
-        <v>30.283566</v>
+        <v>30.2657598</v>
       </c>
       <c r="O72">
-        <v>9.085069799999999</v>
+        <v>9.07972794</v>
       </c>
       <c r="P72">
-        <v>21.1984962</v>
+        <v>21.18603186</v>
       </c>
       <c r="Q72">
-        <v>26.2684962</v>
+        <v>26.25603186</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1879761108984859</v>
+        <v>0.1923202085688892</v>
       </c>
       <c r="T72">
-        <v>3.283512953775656</v>
+        <v>3.383838535078274</v>
       </c>
       <c r="U72">
         <v>0.0503</v>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>25.2961648992245</v>
+        <v>24.93988088655937</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7469,22 +7469,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08077196048497787</v>
+        <v>0.08050408770040998</v>
       </c>
       <c r="C73">
-        <v>10.9575042598457</v>
+        <v>10.62083905166654</v>
       </c>
       <c r="D73">
-        <v>32.0515042598457</v>
+        <v>32.06883905166654</v>
       </c>
       <c r="E73">
-        <v>11.834</v>
+        <v>12.188</v>
       </c>
       <c r="F73">
-        <v>25.134</v>
+        <v>25.488</v>
       </c>
       <c r="G73">
         <v>4.04</v>
@@ -7505,28 +7505,28 @@
         <v>31.53</v>
       </c>
       <c r="M73">
-        <v>1.2642402</v>
+        <v>1.2820464</v>
       </c>
       <c r="N73">
-        <v>30.2657598</v>
+        <v>30.2479536</v>
       </c>
       <c r="O73">
-        <v>9.07972794</v>
+        <v>9.07438608</v>
       </c>
       <c r="P73">
-        <v>21.18603186</v>
+        <v>21.17356752</v>
       </c>
       <c r="Q73">
-        <v>26.25603186</v>
+        <v>26.24356752</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1923202085688892</v>
+        <v>0.1969745989300356</v>
       </c>
       <c r="T73">
-        <v>3.383838535078273</v>
+        <v>3.491330229331077</v>
       </c>
       <c r="U73">
         <v>0.0503</v>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>24.93988088655937</v>
+        <v>24.59349365202383</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7551,22 +7551,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08050408770040998</v>
+        <v>0.08023621491584208</v>
       </c>
       <c r="C74">
-        <v>10.62083905166654</v>
+        <v>10.28419260439254</v>
       </c>
       <c r="D74">
-        <v>32.06883905166654</v>
+        <v>32.08619260439254</v>
       </c>
       <c r="E74">
-        <v>12.188</v>
+        <v>12.542</v>
       </c>
       <c r="F74">
-        <v>25.488</v>
+        <v>25.842</v>
       </c>
       <c r="G74">
         <v>4.04</v>
@@ -7587,28 +7587,28 @@
         <v>31.53</v>
       </c>
       <c r="M74">
-        <v>1.2820464</v>
+        <v>1.2998526</v>
       </c>
       <c r="N74">
-        <v>30.2479536</v>
+        <v>30.2301474</v>
       </c>
       <c r="O74">
-        <v>9.07438608</v>
+        <v>9.06904422</v>
       </c>
       <c r="P74">
-        <v>21.17356752</v>
+        <v>21.16110318</v>
       </c>
       <c r="Q74">
-        <v>26.24356752</v>
+        <v>26.23110318</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1969745989300356</v>
+        <v>0.2019737589475633</v>
       </c>
       <c r="T74">
-        <v>3.491330229331077</v>
+        <v>3.606784271306311</v>
       </c>
       <c r="U74">
         <v>0.0503</v>
@@ -7625,7 +7625,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>24.59349365202383</v>
+        <v>24.25659647870843</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7633,22 +7633,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08023621491584208</v>
+        <v>0.07996834213127418</v>
       </c>
       <c r="C75">
-        <v>10.28419260439254</v>
+        <v>9.947564948496691</v>
       </c>
       <c r="D75">
-        <v>32.08619260439254</v>
+        <v>32.1035649484967</v>
       </c>
       <c r="E75">
-        <v>12.542</v>
+        <v>12.896</v>
       </c>
       <c r="F75">
-        <v>25.842</v>
+        <v>26.19600000000001</v>
       </c>
       <c r="G75">
         <v>4.04</v>
@@ -7669,28 +7669,28 @@
         <v>31.53</v>
       </c>
       <c r="M75">
-        <v>1.2998526</v>
+        <v>1.3176588</v>
       </c>
       <c r="N75">
-        <v>30.2301474</v>
+        <v>30.2123412</v>
       </c>
       <c r="O75">
-        <v>9.06904422</v>
+        <v>9.063702360000001</v>
       </c>
       <c r="P75">
-        <v>21.16110318</v>
+        <v>21.14863884</v>
       </c>
       <c r="Q75">
-        <v>26.23110318</v>
+        <v>26.21863884</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2019737589475633</v>
+        <v>0.2073574697356699</v>
       </c>
       <c r="T75">
-        <v>3.606784271306311</v>
+        <v>3.731119393433485</v>
       </c>
       <c r="U75">
         <v>0.0503</v>
@@ -7707,7 +7707,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>24.25659647870843</v>
+        <v>23.92880463440156</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7715,22 +7715,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07996834213127418</v>
+        <v>0.07970046934670628</v>
       </c>
       <c r="C76">
-        <v>9.947564948496691</v>
+        <v>9.610956114518032</v>
       </c>
       <c r="D76">
-        <v>32.1035649484967</v>
+        <v>32.12095611451804</v>
       </c>
       <c r="E76">
-        <v>12.896</v>
+        <v>13.25</v>
       </c>
       <c r="F76">
-        <v>26.19600000000001</v>
+        <v>26.55</v>
       </c>
       <c r="G76">
         <v>4.04</v>
@@ -7751,28 +7751,28 @@
         <v>31.53</v>
       </c>
       <c r="M76">
-        <v>1.3176588</v>
+        <v>1.335465</v>
       </c>
       <c r="N76">
-        <v>30.2123412</v>
+        <v>30.194535</v>
       </c>
       <c r="O76">
-        <v>9.063702360000001</v>
+        <v>9.058360500000001</v>
       </c>
       <c r="P76">
-        <v>21.14863884</v>
+        <v>21.1361745</v>
       </c>
       <c r="Q76">
-        <v>26.21863884</v>
+        <v>26.2061745</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2073574697356699</v>
+        <v>0.2131718773868251</v>
       </c>
       <c r="T76">
-        <v>3.731119393433485</v>
+        <v>3.865401325330835</v>
       </c>
       <c r="U76">
         <v>0.0503</v>
@@ -7789,7 +7789,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>23.92880463440156</v>
+        <v>23.60975390594287</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7797,22 +7797,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07970046934670628</v>
+        <v>0.07943259656213839</v>
       </c>
       <c r="C77">
-        <v>9.610956114518032</v>
+        <v>9.274366133061811</v>
       </c>
       <c r="D77">
-        <v>32.12095611451804</v>
+        <v>32.13836613306182</v>
       </c>
       <c r="E77">
-        <v>13.25</v>
+        <v>13.604</v>
       </c>
       <c r="F77">
-        <v>26.55</v>
+        <v>26.904</v>
       </c>
       <c r="G77">
         <v>4.04</v>
@@ -7833,28 +7833,28 @@
         <v>31.53</v>
       </c>
       <c r="M77">
-        <v>1.335465</v>
+        <v>1.3532712</v>
       </c>
       <c r="N77">
-        <v>30.194535</v>
+        <v>30.1767288</v>
       </c>
       <c r="O77">
-        <v>9.058360500000001</v>
+        <v>9.053018639999999</v>
       </c>
       <c r="P77">
-        <v>21.1361745</v>
+        <v>21.12371016</v>
       </c>
       <c r="Q77">
-        <v>26.2061745</v>
+        <v>26.19371016</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2131718773868251</v>
+        <v>0.21947081900891</v>
       </c>
       <c r="T77">
-        <v>3.865401325330835</v>
+        <v>4.010873418219631</v>
       </c>
       <c r="U77">
         <v>0.0503</v>
@@ -7871,7 +7871,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>23.60975390594287</v>
+        <v>23.29909924928573</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7879,22 +7879,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07943259656213839</v>
+        <v>0.07916472377757049</v>
       </c>
       <c r="C78">
-        <v>9.274366133061811</v>
+        <v>8.93779503479966</v>
       </c>
       <c r="D78">
-        <v>32.13836613306182</v>
+        <v>32.15579503479967</v>
       </c>
       <c r="E78">
-        <v>13.604</v>
+        <v>13.95800000000001</v>
       </c>
       <c r="F78">
-        <v>26.904</v>
+        <v>27.25800000000001</v>
       </c>
       <c r="G78">
         <v>4.04</v>
@@ -7915,28 +7915,28 @@
         <v>31.53</v>
       </c>
       <c r="M78">
-        <v>1.3532712</v>
+        <v>1.3710774</v>
       </c>
       <c r="N78">
-        <v>30.1767288</v>
+        <v>30.1589226</v>
       </c>
       <c r="O78">
-        <v>9.053018639999999</v>
+        <v>9.04767678</v>
       </c>
       <c r="P78">
-        <v>21.12371016</v>
+        <v>21.11124582</v>
       </c>
       <c r="Q78">
-        <v>26.19371016</v>
+        <v>26.18124582</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.21947081900891</v>
+        <v>0.2263174946850891</v>
       </c>
       <c r="T78">
-        <v>4.010873418219631</v>
+        <v>4.168995258316146</v>
       </c>
       <c r="U78">
         <v>0.0503</v>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>23.29909924928573</v>
+        <v>22.99651354474955</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7961,22 +7961,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07916472377757049</v>
+        <v>0.07889685099300259</v>
       </c>
       <c r="C79">
-        <v>8.93779503479966</v>
+        <v>8.601242850469792</v>
       </c>
       <c r="D79">
-        <v>32.15579503479967</v>
+        <v>32.1732428504698</v>
       </c>
       <c r="E79">
-        <v>13.95800000000001</v>
+        <v>14.312</v>
       </c>
       <c r="F79">
-        <v>27.25800000000001</v>
+        <v>27.61200000000001</v>
       </c>
       <c r="G79">
         <v>4.04</v>
@@ -7997,28 +7997,28 @@
         <v>31.53</v>
       </c>
       <c r="M79">
-        <v>1.3710774</v>
+        <v>1.3888836</v>
       </c>
       <c r="N79">
-        <v>30.1589226</v>
+        <v>30.1411164</v>
       </c>
       <c r="O79">
-        <v>9.04767678</v>
+        <v>9.04233492</v>
       </c>
       <c r="P79">
-        <v>21.11124582</v>
+        <v>21.09878148</v>
       </c>
       <c r="Q79">
-        <v>26.18124582</v>
+        <v>26.16878148</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2263174946850891</v>
+        <v>0.2337865954227391</v>
       </c>
       <c r="T79">
-        <v>4.168995258316146</v>
+        <v>4.34149181114871</v>
       </c>
       <c r="U79">
         <v>0.0503</v>
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>22.99651354474955</v>
+        <v>22.70168644802199</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8043,22 +8043,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07889685099300259</v>
+        <v>0.0786289782084347</v>
       </c>
       <c r="C80">
-        <v>8.601242850469792</v>
+        <v>8.264709610877158</v>
       </c>
       <c r="D80">
-        <v>32.1732428504698</v>
+        <v>32.19070961087716</v>
       </c>
       <c r="E80">
-        <v>14.312</v>
+        <v>14.666</v>
       </c>
       <c r="F80">
-        <v>27.61200000000001</v>
+        <v>27.966</v>
       </c>
       <c r="G80">
         <v>4.04</v>
@@ -8079,28 +8079,28 @@
         <v>31.53</v>
       </c>
       <c r="M80">
-        <v>1.3888836</v>
+        <v>1.4066898</v>
       </c>
       <c r="N80">
-        <v>30.1411164</v>
+        <v>30.1233102</v>
       </c>
       <c r="O80">
-        <v>9.04233492</v>
+        <v>9.03699306</v>
       </c>
       <c r="P80">
-        <v>21.09878148</v>
+        <v>21.08631714</v>
       </c>
       <c r="Q80">
-        <v>26.16878148</v>
+        <v>26.15631714</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2337865954227391</v>
+        <v>0.2419670390877843</v>
       </c>
       <c r="T80">
-        <v>4.34149181114871</v>
+        <v>4.530416607108184</v>
       </c>
       <c r="U80">
         <v>0.0503</v>
@@ -8117,7 +8117,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>22.70168644802199</v>
+        <v>22.41432332842678</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8125,22 +8125,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0786289782084347</v>
+        <v>0.07836110542386679</v>
       </c>
       <c r="C81">
-        <v>8.264709610877158</v>
+        <v>7.928195346893645</v>
       </c>
       <c r="D81">
-        <v>32.19070961087716</v>
+        <v>32.20819534689365</v>
       </c>
       <c r="E81">
-        <v>14.666</v>
+        <v>15.02000000000001</v>
       </c>
       <c r="F81">
-        <v>27.966</v>
+        <v>28.32000000000001</v>
       </c>
       <c r="G81">
         <v>4.04</v>
@@ -8161,28 +8161,28 @@
         <v>31.53</v>
       </c>
       <c r="M81">
-        <v>1.4066898</v>
+        <v>1.424496</v>
       </c>
       <c r="N81">
-        <v>30.1233102</v>
+        <v>30.105504</v>
       </c>
       <c r="O81">
-        <v>9.03699306</v>
+        <v>9.031651199999999</v>
       </c>
       <c r="P81">
-        <v>21.08631714</v>
+        <v>21.0738528</v>
       </c>
       <c r="Q81">
-        <v>26.15631714</v>
+        <v>26.1438528</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2419670390877843</v>
+        <v>0.250965527119334</v>
       </c>
       <c r="T81">
-        <v>4.530416607108184</v>
+        <v>4.738233882663605</v>
       </c>
       <c r="U81">
         <v>0.0503</v>
@@ -8199,7 +8199,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>22.41432332842678</v>
+        <v>22.13414428682144</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8207,22 +8207,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07836110542386679</v>
+        <v>0.0780932326392989</v>
       </c>
       <c r="C82">
-        <v>7.928195346893645</v>
+        <v>7.591700089458278</v>
       </c>
       <c r="D82">
-        <v>32.20819534689365</v>
+        <v>32.22570008945829</v>
       </c>
       <c r="E82">
-        <v>15.02000000000001</v>
+        <v>15.37400000000001</v>
       </c>
       <c r="F82">
-        <v>28.32000000000001</v>
+        <v>28.67400000000001</v>
       </c>
       <c r="G82">
         <v>4.04</v>
@@ -8243,28 +8243,28 @@
         <v>31.53</v>
       </c>
       <c r="M82">
-        <v>1.424496</v>
+        <v>1.4423022</v>
       </c>
       <c r="N82">
-        <v>30.105504</v>
+        <v>30.0876978</v>
       </c>
       <c r="O82">
-        <v>9.031651199999999</v>
+        <v>9.026309339999999</v>
       </c>
       <c r="P82">
-        <v>21.0738528</v>
+        <v>21.06138846</v>
       </c>
       <c r="Q82">
-        <v>26.1438528</v>
+        <v>26.13138846</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.250965527119334</v>
+        <v>0.2609112244173627</v>
       </c>
       <c r="T82">
-        <v>4.738233882663605</v>
+        <v>4.967926660909071</v>
       </c>
       <c r="U82">
         <v>0.0503</v>
@@ -8281,7 +8281,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>22.13414428682144</v>
+        <v>21.8608832462434</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8289,22 +8289,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.0780932326392989</v>
+        <v>0.07782535985473102</v>
       </c>
       <c r="C83">
-        <v>7.591700089458278</v>
+        <v>7.255223869577335</v>
       </c>
       <c r="D83">
-        <v>32.22570008945829</v>
+        <v>32.24322386957734</v>
       </c>
       <c r="E83">
-        <v>15.37400000000001</v>
+        <v>15.72800000000001</v>
       </c>
       <c r="F83">
-        <v>28.67400000000001</v>
+        <v>29.02800000000001</v>
       </c>
       <c r="G83">
         <v>4.04</v>
@@ -8325,28 +8325,28 @@
         <v>31.53</v>
       </c>
       <c r="M83">
-        <v>1.4423022</v>
+        <v>1.4601084</v>
       </c>
       <c r="N83">
-        <v>30.0876978</v>
+        <v>30.0698916</v>
       </c>
       <c r="O83">
-        <v>9.026309339999999</v>
+        <v>9.020967479999999</v>
       </c>
       <c r="P83">
-        <v>21.06138846</v>
+        <v>21.04892412</v>
       </c>
       <c r="Q83">
-        <v>26.13138846</v>
+        <v>26.11892412</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2609112244173627</v>
+        <v>0.2719619991929502</v>
       </c>
       <c r="T83">
-        <v>4.967926660909071</v>
+        <v>5.223140858959589</v>
       </c>
       <c r="U83">
         <v>0.0503</v>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>21.8608832462434</v>
+        <v>21.59428710909409</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8371,22 +8371,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07782535985473102</v>
+        <v>0.07755748707016311</v>
       </c>
       <c r="C84">
-        <v>7.255223869577335</v>
+        <v>6.918766718324594</v>
       </c>
       <c r="D84">
-        <v>32.24322386957734</v>
+        <v>32.2607667183246</v>
       </c>
       <c r="E84">
-        <v>15.72800000000001</v>
+        <v>16.08200000000001</v>
       </c>
       <c r="F84">
-        <v>29.02800000000001</v>
+        <v>29.38200000000001</v>
       </c>
       <c r="G84">
         <v>4.04</v>
@@ -8407,28 +8407,28 @@
         <v>31.53</v>
       </c>
       <c r="M84">
-        <v>1.4601084</v>
+        <v>1.4779146</v>
       </c>
       <c r="N84">
-        <v>30.0698916</v>
+        <v>30.0520854</v>
       </c>
       <c r="O84">
-        <v>9.020967479999999</v>
+        <v>9.01562562</v>
       </c>
       <c r="P84">
-        <v>21.04892412</v>
+        <v>21.03645978</v>
       </c>
       <c r="Q84">
-        <v>26.11892412</v>
+        <v>26.10645978</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2719619991929502</v>
+        <v>0.2843128651186067</v>
       </c>
       <c r="T84">
-        <v>5.223140858959589</v>
+        <v>5.508380256780756</v>
       </c>
       <c r="U84">
         <v>0.0503</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>21.59428710909409</v>
+        <v>21.33411497524958</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8453,22 +8453,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07755748707016311</v>
+        <v>0.07728961428559522</v>
       </c>
       <c r="C85">
-        <v>6.918766718324594</v>
+        <v>6.582328666841516</v>
       </c>
       <c r="D85">
-        <v>32.2607667183246</v>
+        <v>32.27832866684152</v>
       </c>
       <c r="E85">
-        <v>16.08200000000001</v>
+        <v>16.43600000000001</v>
       </c>
       <c r="F85">
-        <v>29.38200000000001</v>
+        <v>29.73600000000001</v>
       </c>
       <c r="G85">
         <v>4.04</v>
@@ -8489,28 +8489,28 @@
         <v>31.53</v>
       </c>
       <c r="M85">
-        <v>1.4779146</v>
+        <v>1.4957208</v>
       </c>
       <c r="N85">
-        <v>30.0520854</v>
+        <v>30.0342792</v>
       </c>
       <c r="O85">
-        <v>9.01562562</v>
+        <v>9.01028376</v>
       </c>
       <c r="P85">
-        <v>21.03645978</v>
+        <v>21.02399544</v>
       </c>
       <c r="Q85">
-        <v>26.10645978</v>
+        <v>26.09399544</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2843128651186067</v>
+        <v>0.2982075892849703</v>
       </c>
       <c r="T85">
-        <v>5.508380256780756</v>
+        <v>5.829274579329569</v>
       </c>
       <c r="U85">
         <v>0.0503</v>
@@ -8527,7 +8527,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>21.33411497524958</v>
+        <v>21.08013741602042</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8535,22 +8535,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07728961428559522</v>
+        <v>0.07702174150102734</v>
       </c>
       <c r="C86">
-        <v>6.582328666841519</v>
+        <v>6.245909746337368</v>
       </c>
       <c r="D86">
-        <v>32.27832866684152</v>
+        <v>32.29590974633737</v>
       </c>
       <c r="E86">
-        <v>16.436</v>
+        <v>16.79</v>
       </c>
       <c r="F86">
-        <v>29.736</v>
+        <v>30.09</v>
       </c>
       <c r="G86">
         <v>4.04</v>
@@ -8571,28 +8571,28 @@
         <v>31.53</v>
       </c>
       <c r="M86">
-        <v>1.4957208</v>
+        <v>1.513527</v>
       </c>
       <c r="N86">
-        <v>30.0342792</v>
+        <v>30.016473</v>
       </c>
       <c r="O86">
-        <v>9.01028376</v>
+        <v>9.0049419</v>
       </c>
       <c r="P86">
-        <v>21.02399544</v>
+        <v>21.0115311</v>
       </c>
       <c r="Q86">
-        <v>26.09399544</v>
+        <v>26.0815311</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2982075892849701</v>
+        <v>0.3139549433401822</v>
       </c>
       <c r="T86">
-        <v>5.829274579329565</v>
+        <v>6.192954811551552</v>
       </c>
       <c r="U86">
         <v>0.0503</v>
@@ -8609,7 +8609,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>21.08013741602042</v>
+        <v>20.83213579936136</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8617,22 +8617,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07702174150102734</v>
+        <v>0.07675386871645942</v>
       </c>
       <c r="C87">
-        <v>6.245909746337368</v>
+        <v>5.909509988089486</v>
       </c>
       <c r="D87">
-        <v>32.29590974633737</v>
+        <v>32.31350998808949</v>
       </c>
       <c r="E87">
-        <v>16.79</v>
+        <v>17.14400000000001</v>
       </c>
       <c r="F87">
-        <v>30.09</v>
+        <v>30.44400000000001</v>
       </c>
       <c r="G87">
         <v>4.04</v>
@@ -8653,28 +8653,28 @@
         <v>31.53</v>
       </c>
       <c r="M87">
-        <v>1.513527</v>
+        <v>1.5313332</v>
       </c>
       <c r="N87">
-        <v>30.016473</v>
+        <v>29.9986668</v>
       </c>
       <c r="O87">
-        <v>9.0049419</v>
+        <v>8.999600040000001</v>
       </c>
       <c r="P87">
-        <v>21.0115311</v>
+        <v>20.99906676</v>
       </c>
       <c r="Q87">
-        <v>26.0815311</v>
+        <v>26.06906676</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3139549433401822</v>
+        <v>0.3319519194032816</v>
       </c>
       <c r="T87">
-        <v>6.192954811551552</v>
+        <v>6.608589362662395</v>
       </c>
       <c r="U87">
         <v>0.0503</v>
@@ -8691,7 +8691,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>20.83213579936136</v>
+        <v>20.58990166215948</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8699,22 +8699,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07675386871645942</v>
+        <v>0.07648599593189154</v>
       </c>
       <c r="C88">
-        <v>5.909509988089486</v>
+        <v>5.573129423443408</v>
       </c>
       <c r="D88">
-        <v>32.31350998808949</v>
+        <v>32.33112942344341</v>
       </c>
       <c r="E88">
-        <v>17.14400000000001</v>
+        <v>17.498</v>
       </c>
       <c r="F88">
-        <v>30.44400000000001</v>
+        <v>30.79800000000001</v>
       </c>
       <c r="G88">
         <v>4.04</v>
@@ -8735,28 +8735,28 @@
         <v>31.53</v>
       </c>
       <c r="M88">
-        <v>1.5313332</v>
+        <v>1.5491394</v>
       </c>
       <c r="N88">
-        <v>29.9986668</v>
+        <v>29.9808606</v>
       </c>
       <c r="O88">
-        <v>8.999600040000001</v>
+        <v>8.994258179999999</v>
       </c>
       <c r="P88">
-        <v>20.99906676</v>
+        <v>20.98660242</v>
       </c>
       <c r="Q88">
-        <v>26.06906676</v>
+        <v>26.05660242</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3319519194032816</v>
+        <v>0.3527176610145503</v>
       </c>
       <c r="T88">
-        <v>6.608589362662395</v>
+        <v>7.088167690867214</v>
       </c>
       <c r="U88">
         <v>0.0503</v>
@@ -8773,7 +8773,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>20.58990166215948</v>
+        <v>20.35323612581282</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8781,22 +8781,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07648599593189154</v>
+        <v>0.07621812314732365</v>
       </c>
       <c r="C89">
-        <v>5.573129423443408</v>
+        <v>5.236768083813065</v>
       </c>
       <c r="D89">
-        <v>32.33112942344341</v>
+        <v>32.34876808381307</v>
       </c>
       <c r="E89">
-        <v>17.498</v>
+        <v>17.852</v>
       </c>
       <c r="F89">
-        <v>30.79800000000001</v>
+        <v>31.152</v>
       </c>
       <c r="G89">
         <v>4.04</v>
@@ -8817,28 +8817,28 @@
         <v>31.53</v>
       </c>
       <c r="M89">
-        <v>1.5491394</v>
+        <v>1.5669456</v>
       </c>
       <c r="N89">
-        <v>29.9808606</v>
+        <v>29.9630544</v>
       </c>
       <c r="O89">
-        <v>8.994258179999999</v>
+        <v>8.98891632</v>
       </c>
       <c r="P89">
-        <v>20.98660242</v>
+        <v>20.97413808</v>
       </c>
       <c r="Q89">
-        <v>26.05660242</v>
+        <v>26.04413808</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3527176610145503</v>
+        <v>0.3769443595610304</v>
       </c>
       <c r="T89">
-        <v>7.088167690867214</v>
+        <v>7.647675740439502</v>
       </c>
       <c r="U89">
         <v>0.0503</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>20.35323612581282</v>
+        <v>20.12194935165586</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8863,22 +8863,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07621812314732365</v>
+        <v>0.07595025036275575</v>
       </c>
       <c r="C90">
-        <v>5.236768083813065</v>
+        <v>4.900426000681012</v>
       </c>
       <c r="D90">
-        <v>32.34876808381307</v>
+        <v>32.36642600068102</v>
       </c>
       <c r="E90">
-        <v>17.852</v>
+        <v>18.206</v>
       </c>
       <c r="F90">
-        <v>31.152</v>
+        <v>31.506</v>
       </c>
       <c r="G90">
         <v>4.04</v>
@@ -8899,28 +8899,28 @@
         <v>31.53</v>
       </c>
       <c r="M90">
-        <v>1.5669456</v>
+        <v>1.5847518</v>
       </c>
       <c r="N90">
-        <v>29.9630544</v>
+        <v>29.9452482</v>
       </c>
       <c r="O90">
-        <v>8.98891632</v>
+        <v>8.98357446</v>
       </c>
       <c r="P90">
-        <v>20.97413808</v>
+        <v>20.96167374</v>
       </c>
       <c r="Q90">
-        <v>26.04413808</v>
+        <v>26.03167374</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3769443595610304</v>
+        <v>0.4055759123886887</v>
       </c>
       <c r="T90">
-        <v>7.647675740439502</v>
+        <v>8.308912526297661</v>
       </c>
       <c r="U90">
         <v>0.0503</v>
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>20.12194935165586</v>
+        <v>19.89586003309793</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8945,22 +8945,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07595025036275575</v>
+        <v>0.07568237757818785</v>
       </c>
       <c r="C91">
-        <v>4.900426000681012</v>
+        <v>4.564103205598549</v>
       </c>
       <c r="D91">
-        <v>32.36642600068102</v>
+        <v>32.38410320559856</v>
       </c>
       <c r="E91">
-        <v>18.206</v>
+        <v>18.56000000000001</v>
       </c>
       <c r="F91">
-        <v>31.506</v>
+        <v>31.86000000000001</v>
       </c>
       <c r="G91">
         <v>4.04</v>
@@ -8981,28 +8981,28 @@
         <v>31.53</v>
       </c>
       <c r="M91">
-        <v>1.5847518</v>
+        <v>1.602558</v>
       </c>
       <c r="N91">
-        <v>29.9452482</v>
+        <v>29.927442</v>
       </c>
       <c r="O91">
-        <v>8.98357446</v>
+        <v>8.9782326</v>
       </c>
       <c r="P91">
-        <v>20.96167374</v>
+        <v>20.9492094</v>
       </c>
       <c r="Q91">
-        <v>26.03167374</v>
+        <v>26.0192094</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4055759123886887</v>
+        <v>0.4399337757818785</v>
       </c>
       <c r="T91">
-        <v>8.308912526297661</v>
+        <v>9.102396669327451</v>
       </c>
       <c r="U91">
         <v>0.0503</v>
@@ -9019,7 +9019,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>19.89586003309793</v>
+        <v>19.67479492161906</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9027,22 +9027,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07568237757818785</v>
+        <v>0.07541450479361997</v>
       </c>
       <c r="C92">
-        <v>4.564103205598549</v>
+        <v>4.227799730185957</v>
       </c>
       <c r="D92">
-        <v>32.38410320559856</v>
+        <v>32.40179973018596</v>
       </c>
       <c r="E92">
-        <v>18.56000000000001</v>
+        <v>18.91400000000001</v>
       </c>
       <c r="F92">
-        <v>31.86000000000001</v>
+        <v>32.21400000000001</v>
       </c>
       <c r="G92">
         <v>4.04</v>
@@ -9063,28 +9063,28 @@
         <v>31.53</v>
       </c>
       <c r="M92">
-        <v>1.602558</v>
+        <v>1.6203642</v>
       </c>
       <c r="N92">
-        <v>29.927442</v>
+        <v>29.9096358</v>
       </c>
       <c r="O92">
-        <v>8.9782326</v>
+        <v>8.97289074</v>
       </c>
       <c r="P92">
-        <v>20.9492094</v>
+        <v>20.93674506</v>
       </c>
       <c r="Q92">
-        <v>26.0192094</v>
+        <v>26.00674506</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4399337757818785</v>
+        <v>0.4819267199291108</v>
       </c>
       <c r="T92">
-        <v>9.102396669327451</v>
+        <v>10.07221062191942</v>
       </c>
       <c r="U92">
         <v>0.0503</v>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>19.67479492161906</v>
+        <v>19.45858838401885</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9109,22 +9109,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07541450479361997</v>
+        <v>0.07514663200905206</v>
       </c>
       <c r="C93">
-        <v>4.227799730185957</v>
+        <v>3.891515606132657</v>
       </c>
       <c r="D93">
-        <v>32.40179973018596</v>
+        <v>32.41951560613266</v>
       </c>
       <c r="E93">
-        <v>18.91400000000001</v>
+        <v>19.268</v>
       </c>
       <c r="F93">
-        <v>32.21400000000001</v>
+        <v>32.568</v>
       </c>
       <c r="G93">
         <v>4.04</v>
@@ -9145,28 +9145,28 @@
         <v>31.53</v>
       </c>
       <c r="M93">
-        <v>1.6203642</v>
+        <v>1.6381704</v>
       </c>
       <c r="N93">
-        <v>29.9096358</v>
+        <v>29.8918296</v>
       </c>
       <c r="O93">
-        <v>8.97289074</v>
+        <v>8.967548880000001</v>
       </c>
       <c r="P93">
-        <v>20.93674506</v>
+        <v>20.92428072</v>
       </c>
       <c r="Q93">
-        <v>26.00674506</v>
+        <v>25.99428072</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4819267199291108</v>
+        <v>0.534417900113151</v>
       </c>
       <c r="T93">
-        <v>10.07221062191942</v>
+        <v>11.28447806265938</v>
       </c>
       <c r="U93">
         <v>0.0503</v>
@@ -9183,7 +9183,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>19.45858838401885</v>
+        <v>19.24708198854039</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9191,22 +9191,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07514663200905206</v>
+        <v>0.07487875922448417</v>
       </c>
       <c r="C94">
-        <v>3.891515606132657</v>
+        <v>3.555250865197436</v>
       </c>
       <c r="D94">
-        <v>32.41951560613266</v>
+        <v>32.43725086519744</v>
       </c>
       <c r="E94">
-        <v>19.268</v>
+        <v>19.622</v>
       </c>
       <c r="F94">
-        <v>32.568</v>
+        <v>32.922</v>
       </c>
       <c r="G94">
         <v>4.04</v>
@@ -9227,28 +9227,28 @@
         <v>31.53</v>
       </c>
       <c r="M94">
-        <v>1.6381704</v>
+        <v>1.6559766</v>
       </c>
       <c r="N94">
-        <v>29.8918296</v>
+        <v>29.8740234</v>
       </c>
       <c r="O94">
-        <v>8.967548880000001</v>
+        <v>8.962207020000001</v>
       </c>
       <c r="P94">
-        <v>20.92428072</v>
+        <v>20.91181638</v>
       </c>
       <c r="Q94">
-        <v>25.99428072</v>
+        <v>25.98181638</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.534417900113151</v>
+        <v>0.6019065603497742</v>
       </c>
       <c r="T94">
-        <v>11.28447806265938</v>
+        <v>12.84310762932504</v>
       </c>
       <c r="U94">
         <v>0.0503</v>
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>19.24708198854039</v>
+        <v>19.04012411769587</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9273,22 +9273,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07487875922448417</v>
+        <v>0.07461088643991626</v>
       </c>
       <c r="C95">
-        <v>3.555250865197436</v>
+        <v>3.219005539208595</v>
       </c>
       <c r="D95">
-        <v>32.43725086519744</v>
+        <v>32.45500553920861</v>
       </c>
       <c r="E95">
-        <v>19.622</v>
+        <v>19.97600000000001</v>
       </c>
       <c r="F95">
-        <v>32.922</v>
+        <v>33.27600000000001</v>
       </c>
       <c r="G95">
         <v>4.04</v>
@@ -9309,28 +9309,28 @@
         <v>31.53</v>
       </c>
       <c r="M95">
-        <v>1.6559766</v>
+        <v>1.6737828</v>
       </c>
       <c r="N95">
-        <v>29.8740234</v>
+        <v>29.8562172</v>
       </c>
       <c r="O95">
-        <v>8.962207020000001</v>
+        <v>8.95686516</v>
       </c>
       <c r="P95">
-        <v>20.91181638</v>
+        <v>20.89935204</v>
       </c>
       <c r="Q95">
-        <v>25.98181638</v>
+        <v>25.96935204</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6019065603497742</v>
+        <v>0.6918914406652718</v>
       </c>
       <c r="T95">
-        <v>12.84310762932504</v>
+        <v>14.92128038487926</v>
       </c>
       <c r="U95">
         <v>0.0503</v>
@@ -9347,7 +9347,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>19.04012411769587</v>
+        <v>18.83756960580548</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9355,22 +9355,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07461088643991626</v>
+        <v>0.07434301365534837</v>
       </c>
       <c r="C96">
-        <v>3.219005539208595</v>
+        <v>2.882779660064173</v>
       </c>
       <c r="D96">
-        <v>32.45500553920861</v>
+        <v>32.47277966006418</v>
       </c>
       <c r="E96">
-        <v>19.97600000000001</v>
+        <v>20.33000000000001</v>
       </c>
       <c r="F96">
-        <v>33.27600000000001</v>
+        <v>33.63000000000001</v>
       </c>
       <c r="G96">
         <v>4.04</v>
@@ -9391,28 +9391,28 @@
         <v>31.53</v>
       </c>
       <c r="M96">
-        <v>1.6737828</v>
+        <v>1.691589</v>
       </c>
       <c r="N96">
-        <v>29.8562172</v>
+        <v>29.838411</v>
       </c>
       <c r="O96">
-        <v>8.95686516</v>
+        <v>8.9515233</v>
       </c>
       <c r="P96">
-        <v>20.89935204</v>
+        <v>20.8868877</v>
       </c>
       <c r="Q96">
-        <v>25.96935204</v>
+        <v>25.9568877</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6918914406652718</v>
+        <v>0.8178702731069685</v>
       </c>
       <c r="T96">
-        <v>14.92128038487926</v>
+        <v>17.83072224265517</v>
       </c>
       <c r="U96">
         <v>0.0503</v>
@@ -9429,7 +9429,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>18.83756960580548</v>
+        <v>18.63927939942858</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9437,22 +9437,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07434301365534837</v>
+        <v>0.07407514087078049</v>
       </c>
       <c r="C97">
-        <v>2.882779660064173</v>
+        <v>2.546573259732114</v>
       </c>
       <c r="D97">
-        <v>32.47277966006418</v>
+        <v>32.49057325973212</v>
       </c>
       <c r="E97">
-        <v>20.33000000000001</v>
+        <v>20.68400000000001</v>
       </c>
       <c r="F97">
-        <v>33.63000000000001</v>
+        <v>33.98400000000001</v>
       </c>
       <c r="G97">
         <v>4.04</v>
@@ -9473,28 +9473,28 @@
         <v>31.53</v>
       </c>
       <c r="M97">
-        <v>1.691589</v>
+        <v>1.7093952</v>
       </c>
       <c r="N97">
-        <v>29.838411</v>
+        <v>29.8206048</v>
       </c>
       <c r="O97">
-        <v>8.9515233</v>
+        <v>8.94618144</v>
       </c>
       <c r="P97">
-        <v>20.8868877</v>
+        <v>20.87442336</v>
       </c>
       <c r="Q97">
-        <v>25.9568877</v>
+        <v>25.94442336</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8178702731069685</v>
+        <v>1.006838521769514</v>
       </c>
       <c r="T97">
-        <v>17.83072224265517</v>
+        <v>22.19488502931903</v>
       </c>
       <c r="U97">
         <v>0.0503</v>
@@ -9511,7 +9511,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>18.63927939942858</v>
+        <v>18.44512023901787</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9519,22 +9519,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07407514087078047</v>
+        <v>0.07380726808621259</v>
       </c>
       <c r="C98">
-        <v>2.546573259732128</v>
+        <v>2.210386370250475</v>
       </c>
       <c r="D98">
-        <v>32.49057325973213</v>
+        <v>32.50838637025048</v>
       </c>
       <c r="E98">
-        <v>20.684</v>
+        <v>21.03800000000001</v>
       </c>
       <c r="F98">
-        <v>33.984</v>
+        <v>34.33800000000001</v>
       </c>
       <c r="G98">
         <v>4.04</v>
@@ -9555,28 +9555,28 @@
         <v>31.53</v>
       </c>
       <c r="M98">
-        <v>1.7093952</v>
+        <v>1.7272014</v>
       </c>
       <c r="N98">
-        <v>29.8206048</v>
+        <v>29.8027986</v>
       </c>
       <c r="O98">
-        <v>8.94618144</v>
+        <v>8.94083958</v>
       </c>
       <c r="P98">
-        <v>20.87442336</v>
+        <v>20.86195902</v>
       </c>
       <c r="Q98">
-        <v>25.94442336</v>
+        <v>25.93195902</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.006838521769511</v>
+        <v>1.321785602873752</v>
       </c>
       <c r="T98">
-        <v>22.19488502931897</v>
+        <v>29.46848967375871</v>
       </c>
       <c r="U98">
         <v>0.0503</v>
@@ -9593,7 +9593,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>18.44512023901787</v>
+        <v>18.25496436026511</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9601,22 +9601,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07380726808621259</v>
+        <v>0.07353939530164469</v>
       </c>
       <c r="C99">
-        <v>2.210386370250475</v>
+        <v>1.874219023727605</v>
       </c>
       <c r="D99">
-        <v>32.50838637025048</v>
+        <v>32.52621902372761</v>
       </c>
       <c r="E99">
-        <v>21.03800000000001</v>
+        <v>21.39200000000001</v>
       </c>
       <c r="F99">
-        <v>34.33800000000001</v>
+        <v>34.69200000000001</v>
       </c>
       <c r="G99">
         <v>4.04</v>
@@ -9637,28 +9637,28 @@
         <v>31.53</v>
       </c>
       <c r="M99">
-        <v>1.7272014</v>
+        <v>1.7450076</v>
       </c>
       <c r="N99">
-        <v>29.8027986</v>
+        <v>29.7849924</v>
       </c>
       <c r="O99">
-        <v>8.94083958</v>
+        <v>8.935497719999999</v>
       </c>
       <c r="P99">
-        <v>20.86195902</v>
+        <v>20.84949468</v>
       </c>
       <c r="Q99">
-        <v>25.93195902</v>
+        <v>25.91949468</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.321785602873752</v>
+        <v>1.951679765082233</v>
       </c>
       <c r="T99">
-        <v>29.46848967375871</v>
+        <v>44.01569896263818</v>
       </c>
       <c r="U99">
         <v>0.0503</v>
@@ -9675,7 +9675,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>18.25496436026511</v>
+        <v>18.06868921373179</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9683,22 +9683,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07353939530164469</v>
+        <v>0.0732715225170768</v>
       </c>
       <c r="C100">
-        <v>1.874219023727605</v>
+        <v>1.538071252342341</v>
       </c>
       <c r="D100">
-        <v>32.52621902372761</v>
+        <v>32.54407125234235</v>
       </c>
       <c r="E100">
-        <v>21.39200000000001</v>
+        <v>21.74600000000001</v>
       </c>
       <c r="F100">
-        <v>34.69200000000001</v>
+        <v>35.04600000000001</v>
       </c>
       <c r="G100">
         <v>4.04</v>
@@ -9719,28 +9719,28 @@
         <v>31.53</v>
       </c>
       <c r="M100">
-        <v>1.7450076</v>
+        <v>1.7628138</v>
       </c>
       <c r="N100">
-        <v>29.7849924</v>
+        <v>29.7671862</v>
       </c>
       <c r="O100">
-        <v>8.935497719999999</v>
+        <v>8.930155859999999</v>
       </c>
       <c r="P100">
-        <v>20.84949468</v>
+        <v>20.83703034</v>
       </c>
       <c r="Q100">
-        <v>25.91949468</v>
+        <v>25.90703034</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.951679765082233</v>
+        <v>3.841362251707676</v>
       </c>
       <c r="T100">
-        <v>44.01569896263818</v>
+        <v>87.65732682927661</v>
       </c>
       <c r="U100">
         <v>0.0503</v>
@@ -9757,91 +9757,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>18.06868921373179</v>
+        <v>17.88617720147187</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.0732715225170768</v>
-      </c>
-      <c r="C101">
-        <v>1.538071252342341</v>
-      </c>
-      <c r="D101">
-        <v>32.54407125234235</v>
-      </c>
-      <c r="E101">
-        <v>21.74600000000001</v>
-      </c>
-      <c r="F101">
-        <v>35.04600000000001</v>
-      </c>
-      <c r="G101">
-        <v>4.04</v>
-      </c>
-      <c r="H101">
-        <v>22.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>36.6</v>
-      </c>
-      <c r="K101">
-        <v>5.07</v>
-      </c>
-      <c r="L101">
-        <v>31.53</v>
-      </c>
-      <c r="M101">
-        <v>1.7628138</v>
-      </c>
-      <c r="N101">
-        <v>29.7671862</v>
-      </c>
-      <c r="O101">
-        <v>8.930155859999999</v>
-      </c>
-      <c r="P101">
-        <v>20.83703034</v>
-      </c>
-      <c r="Q101">
-        <v>25.90703034</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.841362251707676</v>
-      </c>
-      <c r="T101">
-        <v>87.65732682927661</v>
-      </c>
-      <c r="U101">
-        <v>0.0503</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.03521</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Aaa/AAA</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>17.88617720147187</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
